--- a/IDS_Diploma_Batch 2023_Teaching Scheme_Final (1).xlsx
+++ b/IDS_Diploma_Batch 2023_Teaching Scheme_Final (1).xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Projects\exam\Exam-Management-Automation-System\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67A605FD-E8FB-4E7D-A9BC-894E44BEFE6E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9C451D8-A09B-4013-975A-178B50DB6330}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="138">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="89" uniqueCount="85">
   <si>
     <t>TEACHING &amp; EXAMINATION SCHEME FOR DIPLOMA IN CIVIL ENGINEERING AY: 2023-24</t>
   </si>
@@ -213,9 +213,6 @@
     <t>Soil Mechanics</t>
   </si>
   <si>
-    <t>Language Training Elective Course</t>
-  </si>
-  <si>
     <t>IDCV3010</t>
   </si>
   <si>
@@ -258,16 +255,10 @@
     <t>MOOC Course</t>
   </si>
   <si>
-    <t>Life Skill Elective Course</t>
-  </si>
-  <si>
     <t>IDCV3063</t>
   </si>
   <si>
     <t>Structural Design-II</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Elective </t>
   </si>
   <si>
     <t>TNPC3010</t>
@@ -280,9 +271,6 @@
   </si>
   <si>
     <t>Project/Training</t>
-  </si>
-  <si>
-    <t>Department Elective Courses</t>
   </si>
   <si>
     <t>IDCV3510</t>
@@ -308,159 +296,12 @@
   <si>
     <t>Highway &amp; Traffic Engineering</t>
   </si>
-  <si>
-    <t>CFLS2150</t>
-  </si>
-  <si>
-    <t>Sanskrit: The Language of Vedas</t>
-  </si>
-  <si>
-    <t>CFLS2160</t>
-  </si>
-  <si>
-    <t>Hindi: The Official Language of India</t>
-  </si>
-  <si>
-    <t>CFLS2170</t>
-  </si>
-  <si>
-    <t>Gujarati: The Native Language</t>
-  </si>
-  <si>
-    <t>CFLS2180</t>
-  </si>
-  <si>
-    <t>Kannada: A Prominent Dravidian Language</t>
-  </si>
-  <si>
-    <t>CFLS2190</t>
-  </si>
-  <si>
-    <t>Marathi: An Indo-Aryan language</t>
-  </si>
-  <si>
-    <t>CFLS2200</t>
-  </si>
-  <si>
-    <t>Foreign Language(French)</t>
-  </si>
-  <si>
-    <t>CFLS2210</t>
-  </si>
-  <si>
-    <t>Foreign Language(German)</t>
-  </si>
-  <si>
-    <t>CLSC2040</t>
-  </si>
-  <si>
-    <t>Life Skill Lessons from Bhagavad Gita</t>
-  </si>
-  <si>
-    <t>CLSC2050</t>
-  </si>
-  <si>
-    <t>Learnings from Ramayana</t>
-  </si>
-  <si>
-    <t>CLSC2060</t>
-  </si>
-  <si>
-    <t>Indian Heritage &amp; Culture</t>
-  </si>
-  <si>
-    <t>CLSC2070</t>
-  </si>
-  <si>
-    <t>Indian Classical Music</t>
-  </si>
-  <si>
-    <t>CLSC2080</t>
-  </si>
-  <si>
-    <t>Indian Classical Dance</t>
-  </si>
-  <si>
-    <t>CLSC2090</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Constitutional Empowerment </t>
-  </si>
-  <si>
-    <t>CLSC2100</t>
-  </si>
-  <si>
-    <t>Indian Agriculture</t>
-  </si>
-  <si>
-    <t>CLSC2110</t>
-  </si>
-  <si>
-    <t>Indian Heath Science</t>
-  </si>
-  <si>
-    <t>CLSC2120</t>
-  </si>
-  <si>
-    <t>Indian Architecture and Town Planning</t>
-  </si>
-  <si>
-    <t>CLSC2140</t>
-  </si>
-  <si>
-    <t>Mindfulness &amp; Well-being</t>
-  </si>
-  <si>
-    <t>CLSC2150</t>
-  </si>
-  <si>
-    <t>Culinary Life Skills</t>
-  </si>
-  <si>
-    <t>CLSC2160</t>
-  </si>
-  <si>
-    <t>Environmental Sustainability</t>
-  </si>
-  <si>
-    <t>CLSC2170</t>
-  </si>
-  <si>
-    <t>Cyber Space Awareness</t>
-  </si>
-  <si>
-    <t>CLSC2180</t>
-  </si>
-  <si>
-    <t>Essentials of Entrepreneurship</t>
-  </si>
-  <si>
-    <t>SUMMARY SHEET</t>
-  </si>
-  <si>
-    <t>Semester</t>
-  </si>
-  <si>
-    <t>Skill Enhancement Courses/Internship</t>
-  </si>
-  <si>
-    <t>Value Added Courses/Indian Knowledge System</t>
-  </si>
-  <si>
-    <t>Research Project/On Job Training</t>
-  </si>
-  <si>
-    <t>Total Credit</t>
-  </si>
-  <si>
-    <t>SUMMARY</t>
-  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="11" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -503,22 +344,6 @@
       <sz val="12"/>
       <color theme="1"/>
       <name val="Times New Roman"/>
-    </font>
-    <font>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Cambria"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Cambria"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Arial"/>
     </font>
   </fonts>
   <fills count="5">
@@ -648,7 +473,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="31">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -704,66 +529,32 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -992,16 +783,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="33"/>
-      <c r="B1" s="34"/>
-      <c r="C1" s="34"/>
-      <c r="D1" s="34"/>
-      <c r="E1" s="34"/>
-      <c r="F1" s="34"/>
-      <c r="G1" s="34"/>
-      <c r="H1" s="34"/>
-      <c r="I1" s="34"/>
-      <c r="J1" s="31"/>
+      <c r="A1" s="25"/>
+      <c r="B1" s="24"/>
+      <c r="C1" s="24"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="26"/>
       <c r="K1" s="1"/>
       <c r="L1" s="1"/>
       <c r="M1" s="1"/>
@@ -1013,16 +804,16 @@
       <c r="S1" s="1"/>
     </row>
     <row r="2" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="33"/>
-      <c r="B2" s="34"/>
-      <c r="C2" s="34"/>
-      <c r="D2" s="34"/>
-      <c r="E2" s="34"/>
-      <c r="F2" s="34"/>
-      <c r="G2" s="34"/>
-      <c r="H2" s="34"/>
-      <c r="I2" s="34"/>
-      <c r="J2" s="31"/>
+      <c r="A2" s="25"/>
+      <c r="B2" s="24"/>
+      <c r="C2" s="24"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="26"/>
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
@@ -1034,18 +825,18 @@
       <c r="S2" s="1"/>
     </row>
     <row r="3" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="35" t="s">
+      <c r="A3" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B3" s="34"/>
-      <c r="C3" s="34"/>
-      <c r="D3" s="34"/>
-      <c r="E3" s="34"/>
-      <c r="F3" s="34"/>
-      <c r="G3" s="34"/>
-      <c r="H3" s="34"/>
-      <c r="I3" s="34"/>
-      <c r="J3" s="31"/>
+      <c r="B3" s="24"/>
+      <c r="C3" s="24"/>
+      <c r="D3" s="24"/>
+      <c r="E3" s="24"/>
+      <c r="F3" s="24"/>
+      <c r="G3" s="24"/>
+      <c r="H3" s="24"/>
+      <c r="I3" s="24"/>
+      <c r="J3" s="26"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
@@ -1057,24 +848,24 @@
       <c r="S3" s="1"/>
     </row>
     <row r="4" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="36" t="s">
+      <c r="A4" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="B4" s="36" t="s">
+      <c r="B4" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="C4" s="36" t="s">
+      <c r="C4" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="D4" s="40" t="s">
+      <c r="D4" s="30" t="s">
         <v>4</v>
       </c>
-      <c r="E4" s="34"/>
-      <c r="F4" s="34"/>
-      <c r="G4" s="34"/>
-      <c r="H4" s="34"/>
-      <c r="I4" s="34"/>
-      <c r="J4" s="31"/>
+      <c r="E4" s="24"/>
+      <c r="F4" s="24"/>
+      <c r="G4" s="24"/>
+      <c r="H4" s="24"/>
+      <c r="I4" s="24"/>
+      <c r="J4" s="26"/>
       <c r="K4" s="1"/>
       <c r="L4" s="1"/>
       <c r="M4" s="1"/>
@@ -1086,22 +877,22 @@
       <c r="S4" s="1"/>
     </row>
     <row r="5" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="37"/>
-      <c r="B5" s="37"/>
-      <c r="C5" s="37"/>
-      <c r="D5" s="40" t="s">
+      <c r="A5" s="22"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="E5" s="31"/>
-      <c r="F5" s="40" t="s">
+      <c r="E5" s="26"/>
+      <c r="F5" s="30" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="31"/>
-      <c r="H5" s="40" t="s">
+      <c r="G5" s="26"/>
+      <c r="H5" s="30" t="s">
         <v>7</v>
       </c>
-      <c r="I5" s="31"/>
-      <c r="J5" s="36" t="s">
+      <c r="I5" s="26"/>
+      <c r="J5" s="28" t="s">
         <v>8</v>
       </c>
       <c r="K5" s="1"/>
@@ -1115,9 +906,9 @@
       <c r="S5" s="1"/>
     </row>
     <row r="6" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="38"/>
-      <c r="B6" s="38"/>
-      <c r="C6" s="38"/>
+      <c r="A6" s="23"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="23"/>
       <c r="D6" s="2" t="s">
         <v>9</v>
       </c>
@@ -1136,7 +927,7 @@
       <c r="I6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="J6" s="38"/>
+      <c r="J6" s="23"/>
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="1"/>
@@ -1148,7 +939,7 @@
       <c r="S6" s="1"/>
     </row>
     <row r="7" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="39">
+      <c r="A7" s="21">
         <v>1</v>
       </c>
       <c r="B7" s="3" t="s">
@@ -1190,7 +981,7 @@
       <c r="S7" s="6"/>
     </row>
     <row r="8" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="37"/>
+      <c r="A8" s="22"/>
       <c r="B8" s="3" t="s">
         <v>13</v>
       </c>
@@ -1230,7 +1021,7 @@
       <c r="S8" s="6"/>
     </row>
     <row r="9" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="37"/>
+      <c r="A9" s="22"/>
       <c r="B9" s="3" t="s">
         <v>15</v>
       </c>
@@ -1270,7 +1061,7 @@
       <c r="S9" s="6"/>
     </row>
     <row r="10" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="37"/>
+      <c r="A10" s="22"/>
       <c r="B10" s="3" t="s">
         <v>17</v>
       </c>
@@ -1310,7 +1101,7 @@
       <c r="S10" s="6"/>
     </row>
     <row r="11" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="37"/>
+      <c r="A11" s="22"/>
       <c r="B11" s="3" t="s">
         <v>19</v>
       </c>
@@ -1350,7 +1141,7 @@
       <c r="S11" s="6"/>
     </row>
     <row r="12" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="37"/>
+      <c r="A12" s="22"/>
       <c r="B12" s="4" t="s">
         <v>21</v>
       </c>
@@ -1390,19 +1181,16 @@
       <c r="S12" s="6"/>
     </row>
     <row r="13" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="38"/>
+      <c r="A13" s="23"/>
       <c r="B13" s="8"/>
       <c r="C13" s="8"/>
-      <c r="D13" s="41"/>
-      <c r="E13" s="34"/>
-      <c r="F13" s="34"/>
-      <c r="G13" s="34"/>
-      <c r="H13" s="34"/>
-      <c r="I13" s="31"/>
-      <c r="J13" s="11">
-        <f>SUM(J7:J12)</f>
-        <v>850</v>
-      </c>
+      <c r="D13" s="19"/>
+      <c r="E13" s="24"/>
+      <c r="F13" s="24"/>
+      <c r="G13" s="24"/>
+      <c r="H13" s="24"/>
+      <c r="I13" s="26"/>
+      <c r="J13" s="11"/>
       <c r="K13" s="6"/>
       <c r="L13" s="6"/>
       <c r="M13" s="6"/>
@@ -1414,7 +1202,7 @@
       <c r="S13" s="6"/>
     </row>
     <row r="14" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="39">
+      <c r="A14" s="21">
         <v>2</v>
       </c>
       <c r="B14" s="12" t="s">
@@ -1456,7 +1244,7 @@
       <c r="S14" s="6"/>
     </row>
     <row r="15" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="37"/>
+      <c r="A15" s="22"/>
       <c r="B15" s="12" t="s">
         <v>25</v>
       </c>
@@ -1496,7 +1284,7 @@
       <c r="S15" s="6"/>
     </row>
     <row r="16" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="37"/>
+      <c r="A16" s="22"/>
       <c r="B16" s="12" t="s">
         <v>27</v>
       </c>
@@ -1536,7 +1324,7 @@
       <c r="S16" s="6"/>
     </row>
     <row r="17" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="37"/>
+      <c r="A17" s="22"/>
       <c r="B17" s="12" t="s">
         <v>29</v>
       </c>
@@ -1576,7 +1364,7 @@
       <c r="S17" s="6"/>
     </row>
     <row r="18" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="37"/>
+      <c r="A18" s="22"/>
       <c r="B18" s="12" t="s">
         <v>31</v>
       </c>
@@ -1616,7 +1404,7 @@
       <c r="S18" s="6"/>
     </row>
     <row r="19" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="37"/>
+      <c r="A19" s="22"/>
       <c r="B19" s="4" t="s">
         <v>33</v>
       </c>
@@ -1656,19 +1444,16 @@
       <c r="S19" s="6"/>
     </row>
     <row r="20" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="38"/>
+      <c r="A20" s="23"/>
       <c r="B20" s="3"/>
       <c r="C20" s="5"/>
-      <c r="D20" s="41"/>
-      <c r="E20" s="34"/>
-      <c r="F20" s="34"/>
-      <c r="G20" s="34"/>
-      <c r="H20" s="34"/>
-      <c r="I20" s="31"/>
-      <c r="J20" s="11">
-        <f>SUM(J14:J19)</f>
-        <v>800</v>
-      </c>
+      <c r="D20" s="19"/>
+      <c r="E20" s="24"/>
+      <c r="F20" s="24"/>
+      <c r="G20" s="24"/>
+      <c r="H20" s="24"/>
+      <c r="I20" s="26"/>
+      <c r="J20" s="11"/>
       <c r="K20" s="6"/>
       <c r="L20" s="6"/>
       <c r="M20" s="6"/>
@@ -1680,7 +1465,7 @@
       <c r="S20" s="6"/>
     </row>
     <row r="21" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="39">
+      <c r="A21" s="21">
         <v>3</v>
       </c>
       <c r="B21" s="13" t="s">
@@ -1722,7 +1507,7 @@
       <c r="S21" s="6"/>
     </row>
     <row r="22" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="37"/>
+      <c r="A22" s="22"/>
       <c r="B22" s="12" t="s">
         <v>37</v>
       </c>
@@ -1762,7 +1547,7 @@
       <c r="S22" s="6"/>
     </row>
     <row r="23" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="37"/>
+      <c r="A23" s="22"/>
       <c r="B23" s="12" t="s">
         <v>39</v>
       </c>
@@ -1802,7 +1587,7 @@
       <c r="S23" s="6"/>
     </row>
     <row r="24" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="37"/>
+      <c r="A24" s="22"/>
       <c r="B24" s="12" t="s">
         <v>41</v>
       </c>
@@ -1842,7 +1627,7 @@
       <c r="S24" s="6"/>
     </row>
     <row r="25" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="37"/>
+      <c r="A25" s="22"/>
       <c r="B25" s="6" t="s">
         <v>43</v>
       </c>
@@ -1882,7 +1667,7 @@
       <c r="S25" s="6"/>
     </row>
     <row r="26" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="37"/>
+      <c r="A26" s="22"/>
       <c r="B26" s="6" t="s">
         <v>45</v>
       </c>
@@ -1922,19 +1707,16 @@
       <c r="S26" s="6"/>
     </row>
     <row r="27" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="38"/>
-      <c r="B27" s="41"/>
-      <c r="C27" s="34"/>
-      <c r="D27" s="41"/>
-      <c r="E27" s="34"/>
-      <c r="F27" s="34"/>
-      <c r="G27" s="34"/>
-      <c r="H27" s="34"/>
-      <c r="I27" s="31"/>
-      <c r="J27" s="11">
-        <f>SUM(J21:J26)</f>
-        <v>900</v>
-      </c>
+      <c r="A27" s="23"/>
+      <c r="B27" s="19"/>
+      <c r="C27" s="24"/>
+      <c r="D27" s="19"/>
+      <c r="E27" s="24"/>
+      <c r="F27" s="24"/>
+      <c r="G27" s="24"/>
+      <c r="H27" s="24"/>
+      <c r="I27" s="26"/>
+      <c r="J27" s="11"/>
       <c r="K27" s="6"/>
       <c r="L27" s="6"/>
       <c r="M27" s="6"/>
@@ -1946,7 +1728,7 @@
       <c r="S27" s="6"/>
     </row>
     <row r="28" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="39">
+      <c r="A28" s="21">
         <v>4</v>
       </c>
       <c r="B28" s="13" t="s">
@@ -1988,7 +1770,7 @@
       <c r="S28" s="6"/>
     </row>
     <row r="29" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="37"/>
+      <c r="A29" s="22"/>
       <c r="B29" s="12" t="s">
         <v>49</v>
       </c>
@@ -2028,7 +1810,7 @@
       <c r="S29" s="6"/>
     </row>
     <row r="30" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="37"/>
+      <c r="A30" s="22"/>
       <c r="B30" s="12" t="s">
         <v>51</v>
       </c>
@@ -2068,7 +1850,7 @@
       <c r="S30" s="6"/>
     </row>
     <row r="31" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="37"/>
+      <c r="A31" s="22"/>
       <c r="B31" s="12" t="s">
         <v>53</v>
       </c>
@@ -2108,7 +1890,7 @@
       <c r="S31" s="6"/>
     </row>
     <row r="32" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="37"/>
+      <c r="A32" s="22"/>
       <c r="B32" s="12" t="s">
         <v>55</v>
       </c>
@@ -2148,33 +1930,16 @@
       <c r="S32" s="6"/>
     </row>
     <row r="33" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="37"/>
+      <c r="A33" s="22"/>
       <c r="B33" s="12"/>
-      <c r="C33" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="D33" s="10">
-        <v>100</v>
-      </c>
-      <c r="E33" s="10">
-        <v>0</v>
-      </c>
-      <c r="F33" s="10">
-        <v>0</v>
-      </c>
-      <c r="G33" s="10">
-        <v>0</v>
-      </c>
-      <c r="H33" s="10">
-        <v>0</v>
-      </c>
-      <c r="I33" s="10">
-        <v>0</v>
-      </c>
-      <c r="J33" s="9">
-        <f>SUM(D33:I33)</f>
-        <v>100</v>
-      </c>
+      <c r="C33" s="18"/>
+      <c r="D33" s="10"/>
+      <c r="E33" s="10"/>
+      <c r="F33" s="10"/>
+      <c r="G33" s="10"/>
+      <c r="H33" s="10"/>
+      <c r="I33" s="10"/>
+      <c r="J33" s="9"/>
       <c r="K33" s="6"/>
       <c r="L33" s="6"/>
       <c r="M33" s="6"/>
@@ -2186,19 +1951,16 @@
       <c r="S33" s="6"/>
     </row>
     <row r="34" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="38"/>
-      <c r="B34" s="41"/>
-      <c r="C34" s="34"/>
-      <c r="D34" s="41"/>
-      <c r="E34" s="34"/>
-      <c r="F34" s="34"/>
-      <c r="G34" s="34"/>
-      <c r="H34" s="34"/>
-      <c r="I34" s="31"/>
-      <c r="J34" s="11">
-        <f>SUM(J28:J33)</f>
-        <v>850</v>
-      </c>
+      <c r="A34" s="23"/>
+      <c r="B34" s="19"/>
+      <c r="C34" s="24"/>
+      <c r="D34" s="19"/>
+      <c r="E34" s="24"/>
+      <c r="F34" s="24"/>
+      <c r="G34" s="24"/>
+      <c r="H34" s="24"/>
+      <c r="I34" s="26"/>
+      <c r="J34" s="11"/>
       <c r="K34" s="6"/>
       <c r="L34" s="6"/>
       <c r="M34" s="6"/>
@@ -2210,14 +1972,14 @@
       <c r="S34" s="6"/>
     </row>
     <row r="35" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="39">
+      <c r="A35" s="21">
         <v>5</v>
       </c>
       <c r="B35" s="12" t="s">
+        <v>57</v>
+      </c>
+      <c r="C35" s="4" t="s">
         <v>58</v>
-      </c>
-      <c r="C35" s="4" t="s">
-        <v>59</v>
       </c>
       <c r="D35" s="5">
         <v>40</v>
@@ -2252,12 +2014,12 @@
       <c r="S35" s="6"/>
     </row>
     <row r="36" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="37"/>
+      <c r="A36" s="22"/>
       <c r="B36" s="12" t="s">
+        <v>59</v>
+      </c>
+      <c r="C36" s="8" t="s">
         <v>60</v>
-      </c>
-      <c r="C36" s="8" t="s">
-        <v>61</v>
       </c>
       <c r="D36" s="7">
         <v>40</v>
@@ -2292,12 +2054,12 @@
       <c r="S36" s="6"/>
     </row>
     <row r="37" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="37"/>
+      <c r="A37" s="22"/>
       <c r="B37" s="12" t="s">
+        <v>61</v>
+      </c>
+      <c r="C37" s="3" t="s">
         <v>62</v>
-      </c>
-      <c r="C37" s="3" t="s">
-        <v>63</v>
       </c>
       <c r="D37" s="7">
         <v>40</v>
@@ -2332,12 +2094,12 @@
       <c r="S37" s="6"/>
     </row>
     <row r="38" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="37"/>
+      <c r="A38" s="22"/>
       <c r="B38" s="12" t="s">
+        <v>63</v>
+      </c>
+      <c r="C38" s="12" t="s">
         <v>64</v>
-      </c>
-      <c r="C38" s="12" t="s">
-        <v>65</v>
       </c>
       <c r="D38" s="7">
         <v>40</v>
@@ -2372,12 +2134,12 @@
       <c r="S38" s="6"/>
     </row>
     <row r="39" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="37"/>
+      <c r="A39" s="22"/>
       <c r="B39" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="C39" s="12" t="s">
         <v>66</v>
-      </c>
-      <c r="C39" s="12" t="s">
-        <v>67</v>
       </c>
       <c r="D39" s="7">
         <v>40</v>
@@ -2412,12 +2174,12 @@
       <c r="S39" s="6"/>
     </row>
     <row r="40" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="37"/>
+      <c r="A40" s="22"/>
       <c r="B40" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="C40" s="4" t="s">
         <v>68</v>
-      </c>
-      <c r="C40" s="4" t="s">
-        <v>69</v>
       </c>
       <c r="D40" s="16">
         <v>0</v>
@@ -2452,12 +2214,12 @@
       <c r="S40" s="6"/>
     </row>
     <row r="41" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="37"/>
+      <c r="A41" s="22"/>
       <c r="B41" s="18" t="s">
+        <v>69</v>
+      </c>
+      <c r="C41" s="4" t="s">
         <v>70</v>
-      </c>
-      <c r="C41" s="4" t="s">
-        <v>71</v>
       </c>
       <c r="D41" s="9">
         <v>100</v>
@@ -2478,7 +2240,7 @@
         <v>0</v>
       </c>
       <c r="J41" s="10">
-        <f t="shared" ref="J41:J42" si="5">SUM(D41:I41)</f>
+        <f t="shared" ref="J41" si="5">SUM(D41:I41)</f>
         <v>100</v>
       </c>
       <c r="K41" s="6"/>
@@ -2492,33 +2254,16 @@
       <c r="S41" s="6"/>
     </row>
     <row r="42" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="37"/>
+      <c r="A42" s="22"/>
       <c r="B42" s="18"/>
-      <c r="C42" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="D42" s="10">
-        <v>100</v>
-      </c>
-      <c r="E42" s="10">
-        <v>0</v>
-      </c>
-      <c r="F42" s="10">
-        <v>0</v>
-      </c>
-      <c r="G42" s="10">
-        <v>0</v>
-      </c>
-      <c r="H42" s="10">
-        <v>0</v>
-      </c>
-      <c r="I42" s="10">
-        <v>0</v>
-      </c>
-      <c r="J42" s="9">
-        <f t="shared" si="5"/>
-        <v>100</v>
-      </c>
+      <c r="C42" s="18"/>
+      <c r="D42" s="10"/>
+      <c r="E42" s="10"/>
+      <c r="F42" s="10"/>
+      <c r="G42" s="10"/>
+      <c r="H42" s="10"/>
+      <c r="I42" s="10"/>
+      <c r="J42" s="9"/>
       <c r="K42" s="6"/>
       <c r="L42" s="6"/>
       <c r="M42" s="6"/>
@@ -2530,19 +2275,16 @@
       <c r="S42" s="6"/>
     </row>
     <row r="43" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="38"/>
-      <c r="B43" s="41"/>
-      <c r="C43" s="34"/>
-      <c r="D43" s="41"/>
-      <c r="E43" s="34"/>
-      <c r="F43" s="34"/>
-      <c r="G43" s="34"/>
-      <c r="H43" s="34"/>
-      <c r="I43" s="31"/>
-      <c r="J43" s="11">
-        <f>SUM(J35:J42)</f>
-        <v>1050</v>
-      </c>
+      <c r="A43" s="23"/>
+      <c r="B43" s="19"/>
+      <c r="C43" s="20"/>
+      <c r="D43" s="19"/>
+      <c r="E43" s="29"/>
+      <c r="F43" s="29"/>
+      <c r="G43" s="29"/>
+      <c r="H43" s="29"/>
+      <c r="I43" s="20"/>
+      <c r="J43" s="11"/>
       <c r="K43" s="6"/>
       <c r="L43" s="6"/>
       <c r="M43" s="6"/>
@@ -2554,14 +2296,14 @@
       <c r="S43" s="6"/>
     </row>
     <row r="44" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="39">
+      <c r="A44" s="21">
         <v>6</v>
       </c>
       <c r="B44" s="12" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C44" s="8" t="s">
-        <v>74</v>
+        <v>72</v>
       </c>
       <c r="D44" s="5">
         <v>40</v>
@@ -2596,33 +2338,16 @@
       <c r="S44" s="6"/>
     </row>
     <row r="45" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="37"/>
+      <c r="A45" s="22"/>
       <c r="B45" s="12"/>
-      <c r="C45" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D45" s="7">
-        <v>40</v>
-      </c>
-      <c r="E45" s="7">
-        <v>60</v>
-      </c>
-      <c r="F45" s="7">
-        <v>0</v>
-      </c>
-      <c r="G45" s="7">
-        <v>0</v>
-      </c>
-      <c r="H45" s="7">
-        <v>0</v>
-      </c>
-      <c r="I45" s="7">
-        <v>0</v>
-      </c>
-      <c r="J45" s="5">
-        <f t="shared" si="6"/>
-        <v>100</v>
-      </c>
+      <c r="C45" s="4"/>
+      <c r="D45" s="7"/>
+      <c r="E45" s="7"/>
+      <c r="F45" s="7"/>
+      <c r="G45" s="7"/>
+      <c r="H45" s="7"/>
+      <c r="I45" s="7"/>
+      <c r="J45" s="5"/>
       <c r="K45" s="6"/>
       <c r="L45" s="6"/>
       <c r="M45" s="6"/>
@@ -2634,12 +2359,12 @@
       <c r="S45" s="6"/>
     </row>
     <row r="46" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="37"/>
+      <c r="A46" s="22"/>
       <c r="B46" s="12" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="C46" s="4" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D46" s="7">
         <v>100</v>
@@ -2674,12 +2399,12 @@
       <c r="S46" s="6"/>
     </row>
     <row r="47" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="37"/>
+      <c r="A47" s="22"/>
       <c r="B47" s="12" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="C47" s="4" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="D47" s="7">
         <v>0</v>
@@ -2714,85 +2439,136 @@
       <c r="S47" s="6"/>
     </row>
     <row r="48" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="37"/>
-      <c r="B48" s="5"/>
-      <c r="C48" s="5"/>
-      <c r="D48" s="41"/>
-      <c r="E48" s="34"/>
-      <c r="F48" s="34"/>
-      <c r="G48" s="34"/>
-      <c r="H48" s="34"/>
-      <c r="I48" s="31"/>
-      <c r="J48" s="11">
-        <f>SUM(J44:J47)</f>
-        <v>850</v>
-      </c>
-      <c r="K48" s="6"/>
-      <c r="L48" s="6"/>
-      <c r="M48" s="6"/>
-      <c r="N48" s="6"/>
-      <c r="O48" s="6"/>
-      <c r="P48" s="6"/>
-      <c r="Q48" s="6"/>
-      <c r="R48" s="6"/>
-      <c r="S48" s="6"/>
+      <c r="A48" s="22"/>
+      <c r="B48" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="C48" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D48" s="7">
+        <v>40</v>
+      </c>
+      <c r="E48" s="7">
+        <v>60</v>
+      </c>
+      <c r="F48" s="5">
+        <v>0</v>
+      </c>
+      <c r="G48" s="5">
+        <v>0</v>
+      </c>
+      <c r="H48" s="5">
+        <v>0</v>
+      </c>
+      <c r="I48" s="7">
+        <v>0</v>
+      </c>
+      <c r="J48" s="5">
+        <f t="shared" ref="J48:J51" si="7">+SUM(D48:I48)</f>
+        <v>100</v>
+      </c>
+      <c r="K48" s="1"/>
+      <c r="L48" s="1"/>
+      <c r="M48" s="1"/>
+      <c r="N48" s="1"/>
+      <c r="O48" s="1"/>
+      <c r="P48" s="1"/>
+      <c r="Q48" s="1"/>
+      <c r="R48" s="1"/>
+      <c r="S48" s="1"/>
     </row>
     <row r="49" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="38"/>
-      <c r="B49" s="6"/>
-      <c r="C49" s="6"/>
-      <c r="D49" s="1"/>
-      <c r="E49" s="1"/>
-      <c r="F49" s="1"/>
-      <c r="G49" s="1"/>
-      <c r="H49" s="1"/>
-      <c r="I49" s="1"/>
-      <c r="J49" s="11">
-        <f>SUM(J48,J43,J34,J27,J20,J13,)</f>
-        <v>5300</v>
-      </c>
-      <c r="K49" s="6"/>
-      <c r="L49" s="6"/>
-      <c r="M49" s="6"/>
-      <c r="N49" s="6"/>
-      <c r="O49" s="6"/>
-      <c r="P49" s="6"/>
-      <c r="Q49" s="6"/>
-      <c r="R49" s="6"/>
-      <c r="S49" s="6"/>
+      <c r="A49" s="23"/>
+      <c r="B49" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="C49" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D49" s="7">
+        <v>40</v>
+      </c>
+      <c r="E49" s="7">
+        <v>60</v>
+      </c>
+      <c r="F49" s="5">
+        <v>0</v>
+      </c>
+      <c r="G49" s="5">
+        <v>0</v>
+      </c>
+      <c r="H49" s="5">
+        <v>0</v>
+      </c>
+      <c r="I49" s="7">
+        <v>0</v>
+      </c>
+      <c r="J49" s="5">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+      <c r="K49" s="1"/>
+      <c r="L49" s="1"/>
+      <c r="M49" s="1"/>
+      <c r="N49" s="1"/>
+      <c r="O49" s="1"/>
+      <c r="P49" s="1"/>
+      <c r="Q49" s="1"/>
+      <c r="R49" s="1"/>
+      <c r="S49" s="1"/>
     </row>
     <row r="50" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="17"/>
-      <c r="B50" s="6"/>
-      <c r="C50" s="20" t="s">
-        <v>80</v>
-      </c>
-      <c r="D50" s="21"/>
-      <c r="E50" s="1"/>
-      <c r="F50" s="1"/>
-      <c r="G50" s="1"/>
-      <c r="H50" s="1"/>
-      <c r="I50" s="1"/>
-      <c r="J50" s="22"/>
-      <c r="K50" s="6"/>
-      <c r="L50" s="6"/>
-      <c r="M50" s="6"/>
-      <c r="N50" s="6"/>
-      <c r="O50" s="6"/>
-      <c r="P50" s="6"/>
-      <c r="Q50" s="6"/>
-      <c r="R50" s="6"/>
-      <c r="S50" s="6"/>
+      <c r="A50" s="17">
+        <v>6</v>
+      </c>
+      <c r="B50" s="5" t="s">
+        <v>81</v>
+      </c>
+      <c r="C50" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D50" s="7">
+        <v>40</v>
+      </c>
+      <c r="E50" s="7">
+        <v>60</v>
+      </c>
+      <c r="F50" s="5">
+        <v>0</v>
+      </c>
+      <c r="G50" s="5">
+        <v>0</v>
+      </c>
+      <c r="H50" s="5">
+        <v>0</v>
+      </c>
+      <c r="I50" s="7">
+        <v>0</v>
+      </c>
+      <c r="J50" s="5">
+        <f t="shared" si="7"/>
+        <v>100</v>
+      </c>
+      <c r="K50" s="1"/>
+      <c r="L50" s="1"/>
+      <c r="M50" s="1"/>
+      <c r="N50" s="1"/>
+      <c r="O50" s="1"/>
+      <c r="P50" s="1"/>
+      <c r="Q50" s="1"/>
+      <c r="R50" s="1"/>
+      <c r="S50" s="1"/>
     </row>
     <row r="51" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A51" s="17">
         <v>6</v>
       </c>
       <c r="B51" s="5" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C51" s="3" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="D51" s="7">
         <v>40</v>
@@ -2813,7 +2589,7 @@
         <v>0</v>
       </c>
       <c r="J51" s="5">
-        <f t="shared" ref="J51:J54" si="7">+SUM(D51:I51)</f>
+        <f t="shared" si="7"/>
         <v>100</v>
       </c>
       <c r="K51" s="1"/>
@@ -2827,37 +2603,16 @@
       <c r="S51" s="1"/>
     </row>
     <row r="52" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="17">
-        <v>6</v>
-      </c>
-      <c r="B52" s="5" t="s">
-        <v>83</v>
-      </c>
-      <c r="C52" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="D52" s="7">
-        <v>40</v>
-      </c>
-      <c r="E52" s="7">
-        <v>60</v>
-      </c>
-      <c r="F52" s="5">
-        <v>0</v>
-      </c>
-      <c r="G52" s="5">
-        <v>0</v>
-      </c>
-      <c r="H52" s="5">
-        <v>0</v>
-      </c>
-      <c r="I52" s="7">
-        <v>0</v>
-      </c>
-      <c r="J52" s="5">
-        <f t="shared" si="7"/>
-        <v>100</v>
-      </c>
+      <c r="A52" s="17"/>
+      <c r="B52" s="1"/>
+      <c r="C52" s="1"/>
+      <c r="D52" s="1"/>
+      <c r="E52" s="1"/>
+      <c r="F52" s="1"/>
+      <c r="G52" s="1"/>
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+      <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
       <c r="M52" s="1"/>
@@ -2869,37 +2624,16 @@
       <c r="S52" s="1"/>
     </row>
     <row r="53" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="17">
-        <v>6</v>
-      </c>
-      <c r="B53" s="5" t="s">
-        <v>85</v>
-      </c>
-      <c r="C53" s="3" t="s">
-        <v>86</v>
-      </c>
-      <c r="D53" s="7">
-        <v>40</v>
-      </c>
-      <c r="E53" s="7">
-        <v>60</v>
-      </c>
-      <c r="F53" s="5">
-        <v>0</v>
-      </c>
-      <c r="G53" s="5">
-        <v>0</v>
-      </c>
-      <c r="H53" s="5">
-        <v>0</v>
-      </c>
-      <c r="I53" s="7">
-        <v>0</v>
-      </c>
-      <c r="J53" s="5">
-        <f t="shared" si="7"/>
-        <v>100</v>
-      </c>
+      <c r="A53" s="17"/>
+      <c r="B53" s="1"/>
+      <c r="C53" s="1"/>
+      <c r="D53" s="1"/>
+      <c r="E53" s="1"/>
+      <c r="F53" s="1"/>
+      <c r="G53" s="1"/>
+      <c r="H53" s="1"/>
+      <c r="I53" s="1"/>
+      <c r="J53" s="1"/>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="1"/>
@@ -2911,37 +2645,16 @@
       <c r="S53" s="1"/>
     </row>
     <row r="54" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="17">
-        <v>6</v>
-      </c>
-      <c r="B54" s="5" t="s">
-        <v>87</v>
-      </c>
-      <c r="C54" s="3" t="s">
-        <v>88</v>
-      </c>
-      <c r="D54" s="7">
-        <v>40</v>
-      </c>
-      <c r="E54" s="7">
-        <v>60</v>
-      </c>
-      <c r="F54" s="5">
-        <v>0</v>
-      </c>
-      <c r="G54" s="5">
-        <v>0</v>
-      </c>
-      <c r="H54" s="5">
-        <v>0</v>
-      </c>
-      <c r="I54" s="7">
-        <v>0</v>
-      </c>
-      <c r="J54" s="5">
-        <f t="shared" si="7"/>
-        <v>100</v>
-      </c>
+      <c r="A54" s="1"/>
+      <c r="B54" s="1"/>
+      <c r="C54" s="1"/>
+      <c r="D54" s="1"/>
+      <c r="E54" s="1"/>
+      <c r="F54" s="1"/>
+      <c r="G54" s="1"/>
+      <c r="H54" s="1"/>
+      <c r="I54" s="1"/>
+      <c r="J54" s="1"/>
       <c r="K54" s="1"/>
       <c r="L54" s="1"/>
       <c r="M54" s="1"/>
@@ -2953,18 +2666,16 @@
       <c r="S54" s="1"/>
     </row>
     <row r="55" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="23"/>
-      <c r="B55" s="8"/>
-      <c r="C55" s="20" t="s">
-        <v>57</v>
-      </c>
-      <c r="D55" s="23"/>
-      <c r="E55" s="23"/>
-      <c r="F55" s="23"/>
-      <c r="G55" s="23"/>
-      <c r="H55" s="23"/>
-      <c r="I55" s="23"/>
-      <c r="J55" s="23"/>
+      <c r="A55" s="1"/>
+      <c r="B55" s="1"/>
+      <c r="C55" s="1"/>
+      <c r="D55" s="1"/>
+      <c r="E55" s="1"/>
+      <c r="F55" s="1"/>
+      <c r="G55" s="1"/>
+      <c r="H55" s="1"/>
+      <c r="I55" s="1"/>
+      <c r="J55" s="1"/>
       <c r="K55" s="1"/>
       <c r="L55" s="1"/>
       <c r="M55" s="1"/>
@@ -2976,35 +2687,16 @@
       <c r="S55" s="1"/>
     </row>
     <row r="56" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="10"/>
-      <c r="B56" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="C56" s="4" t="s">
-        <v>90</v>
-      </c>
-      <c r="D56" s="10">
-        <v>100</v>
-      </c>
-      <c r="E56" s="10">
-        <v>0</v>
-      </c>
-      <c r="F56" s="10">
-        <v>0</v>
-      </c>
-      <c r="G56" s="10">
-        <v>0</v>
-      </c>
-      <c r="H56" s="10">
-        <v>0</v>
-      </c>
-      <c r="I56" s="10">
-        <v>0</v>
-      </c>
-      <c r="J56" s="10">
-        <f t="shared" ref="J56:J62" si="8">SUM(D56:I56)</f>
-        <v>100</v>
-      </c>
+      <c r="A56" s="1"/>
+      <c r="B56" s="1"/>
+      <c r="C56" s="1"/>
+      <c r="D56" s="1"/>
+      <c r="E56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="H56" s="1"/>
+      <c r="I56" s="1"/>
+      <c r="J56" s="1"/>
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
       <c r="M56" s="1"/>
@@ -3016,35 +2708,16 @@
       <c r="S56" s="1"/>
     </row>
     <row r="57" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="10"/>
-      <c r="B57" s="4" t="s">
-        <v>91</v>
-      </c>
-      <c r="C57" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="D57" s="10">
-        <v>100</v>
-      </c>
-      <c r="E57" s="10">
-        <v>0</v>
-      </c>
-      <c r="F57" s="10">
-        <v>0</v>
-      </c>
-      <c r="G57" s="10">
-        <v>0</v>
-      </c>
-      <c r="H57" s="10">
-        <v>0</v>
-      </c>
-      <c r="I57" s="10">
-        <v>0</v>
-      </c>
-      <c r="J57" s="10">
-        <f t="shared" si="8"/>
-        <v>100</v>
-      </c>
+      <c r="A57" s="1"/>
+      <c r="B57" s="1"/>
+      <c r="C57" s="1"/>
+      <c r="D57" s="1"/>
+      <c r="E57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="H57" s="1"/>
+      <c r="I57" s="1"/>
+      <c r="J57" s="1"/>
       <c r="K57" s="1"/>
       <c r="L57" s="1"/>
       <c r="M57" s="1"/>
@@ -3056,35 +2729,16 @@
       <c r="S57" s="1"/>
     </row>
     <row r="58" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="10"/>
-      <c r="B58" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="C58" s="4" t="s">
-        <v>94</v>
-      </c>
-      <c r="D58" s="10">
-        <v>100</v>
-      </c>
-      <c r="E58" s="10">
-        <v>0</v>
-      </c>
-      <c r="F58" s="10">
-        <v>0</v>
-      </c>
-      <c r="G58" s="10">
-        <v>0</v>
-      </c>
-      <c r="H58" s="10">
-        <v>0</v>
-      </c>
-      <c r="I58" s="10">
-        <v>0</v>
-      </c>
-      <c r="J58" s="10">
-        <f t="shared" si="8"/>
-        <v>100</v>
-      </c>
+      <c r="A58" s="1"/>
+      <c r="B58" s="1"/>
+      <c r="C58" s="1"/>
+      <c r="D58" s="1"/>
+      <c r="E58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="H58" s="1"/>
+      <c r="I58" s="1"/>
+      <c r="J58" s="1"/>
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="1"/>
@@ -3096,35 +2750,16 @@
       <c r="S58" s="1"/>
     </row>
     <row r="59" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="10"/>
-      <c r="B59" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="C59" s="4" t="s">
-        <v>96</v>
-      </c>
-      <c r="D59" s="10">
-        <v>100</v>
-      </c>
-      <c r="E59" s="10">
-        <v>0</v>
-      </c>
-      <c r="F59" s="10">
-        <v>0</v>
-      </c>
-      <c r="G59" s="10">
-        <v>0</v>
-      </c>
-      <c r="H59" s="10">
-        <v>0</v>
-      </c>
-      <c r="I59" s="10">
-        <v>0</v>
-      </c>
-      <c r="J59" s="10">
-        <f t="shared" si="8"/>
-        <v>100</v>
-      </c>
+      <c r="A59" s="1"/>
+      <c r="B59" s="1"/>
+      <c r="C59" s="1"/>
+      <c r="D59" s="1"/>
+      <c r="E59" s="1"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="H59" s="1"/>
+      <c r="I59" s="1"/>
+      <c r="J59" s="1"/>
       <c r="K59" s="1"/>
       <c r="L59" s="1"/>
       <c r="M59" s="1"/>
@@ -3136,35 +2771,16 @@
       <c r="S59" s="1"/>
     </row>
     <row r="60" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="10"/>
-      <c r="B60" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="C60" s="4" t="s">
-        <v>98</v>
-      </c>
-      <c r="D60" s="10">
-        <v>100</v>
-      </c>
-      <c r="E60" s="10">
-        <v>0</v>
-      </c>
-      <c r="F60" s="10">
-        <v>0</v>
-      </c>
-      <c r="G60" s="10">
-        <v>0</v>
-      </c>
-      <c r="H60" s="10">
-        <v>0</v>
-      </c>
-      <c r="I60" s="10">
-        <v>0</v>
-      </c>
-      <c r="J60" s="10">
-        <f t="shared" si="8"/>
-        <v>100</v>
-      </c>
+      <c r="A60" s="1"/>
+      <c r="B60" s="1"/>
+      <c r="C60" s="1"/>
+      <c r="D60" s="1"/>
+      <c r="E60" s="1"/>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="H60" s="1"/>
+      <c r="I60" s="1"/>
+      <c r="J60" s="1"/>
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
       <c r="M60" s="1"/>
@@ -3176,35 +2792,16 @@
       <c r="S60" s="1"/>
     </row>
     <row r="61" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="10"/>
-      <c r="B61" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="C61" s="4" t="s">
-        <v>100</v>
-      </c>
-      <c r="D61" s="10">
-        <v>100</v>
-      </c>
-      <c r="E61" s="10">
-        <v>0</v>
-      </c>
-      <c r="F61" s="10">
-        <v>0</v>
-      </c>
-      <c r="G61" s="10">
-        <v>0</v>
-      </c>
-      <c r="H61" s="10">
-        <v>0</v>
-      </c>
-      <c r="I61" s="10">
-        <v>0</v>
-      </c>
-      <c r="J61" s="10">
-        <f t="shared" si="8"/>
-        <v>100</v>
-      </c>
+      <c r="A61" s="1"/>
+      <c r="B61" s="1"/>
+      <c r="C61" s="1"/>
+      <c r="D61" s="1"/>
+      <c r="E61" s="1"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="H61" s="1"/>
+      <c r="I61" s="1"/>
+      <c r="J61" s="1"/>
       <c r="K61" s="1"/>
       <c r="L61" s="1"/>
       <c r="M61" s="1"/>
@@ -3216,35 +2813,16 @@
       <c r="S61" s="1"/>
     </row>
     <row r="62" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="10"/>
-      <c r="B62" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="C62" s="4" t="s">
-        <v>102</v>
-      </c>
-      <c r="D62" s="10">
-        <v>100</v>
-      </c>
-      <c r="E62" s="10">
-        <v>0</v>
-      </c>
-      <c r="F62" s="10">
-        <v>0</v>
-      </c>
-      <c r="G62" s="10">
-        <v>0</v>
-      </c>
-      <c r="H62" s="10">
-        <v>0</v>
-      </c>
-      <c r="I62" s="10">
-        <v>0</v>
-      </c>
-      <c r="J62" s="10">
-        <f t="shared" si="8"/>
-        <v>100</v>
-      </c>
+      <c r="A62" s="1"/>
+      <c r="B62" s="1"/>
+      <c r="C62" s="1"/>
+      <c r="D62" s="1"/>
+      <c r="E62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="H62" s="1"/>
+      <c r="I62" s="1"/>
+      <c r="J62" s="1"/>
       <c r="K62" s="1"/>
       <c r="L62" s="1"/>
       <c r="M62" s="1"/>
@@ -3256,18 +2834,16 @@
       <c r="S62" s="1"/>
     </row>
     <row r="63" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="17"/>
-      <c r="B63" s="6"/>
-      <c r="C63" s="20" t="s">
-        <v>72</v>
-      </c>
-      <c r="D63" s="6"/>
-      <c r="E63" s="6"/>
-      <c r="F63" s="6"/>
-      <c r="G63" s="6"/>
-      <c r="H63" s="6"/>
-      <c r="I63" s="6"/>
-      <c r="J63" s="6"/>
+      <c r="A63" s="1"/>
+      <c r="B63" s="1"/>
+      <c r="C63" s="1"/>
+      <c r="D63" s="1"/>
+      <c r="E63" s="1"/>
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="H63" s="1"/>
+      <c r="I63" s="1"/>
+      <c r="J63" s="1"/>
       <c r="K63" s="1"/>
       <c r="L63" s="1"/>
       <c r="M63" s="1"/>
@@ -3279,35 +2855,16 @@
       <c r="S63" s="1"/>
     </row>
     <row r="64" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="17"/>
-      <c r="B64" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="C64" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="D64" s="9">
-        <v>100</v>
-      </c>
-      <c r="E64" s="9">
-        <v>0</v>
-      </c>
-      <c r="F64" s="9">
-        <v>0</v>
-      </c>
-      <c r="G64" s="9">
-        <v>0</v>
-      </c>
-      <c r="H64" s="9">
-        <v>0</v>
-      </c>
-      <c r="I64" s="9">
-        <v>0</v>
-      </c>
-      <c r="J64" s="10">
-        <f t="shared" ref="J64:J78" si="9">SUM(D64:I64)</f>
-        <v>100</v>
-      </c>
+      <c r="A64" s="1"/>
+      <c r="B64" s="1"/>
+      <c r="C64" s="1"/>
+      <c r="D64" s="1"/>
+      <c r="E64" s="1"/>
+      <c r="F64" s="1"/>
+      <c r="G64" s="1"/>
+      <c r="H64" s="1"/>
+      <c r="I64" s="1"/>
+      <c r="J64" s="1"/>
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
       <c r="M64" s="1"/>
@@ -3319,35 +2876,16 @@
       <c r="S64" s="1"/>
     </row>
     <row r="65" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="17"/>
-      <c r="B65" s="4" t="s">
-        <v>105</v>
-      </c>
-      <c r="C65" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="D65" s="9">
-        <v>100</v>
-      </c>
-      <c r="E65" s="9">
-        <v>0</v>
-      </c>
-      <c r="F65" s="9">
-        <v>0</v>
-      </c>
-      <c r="G65" s="9">
-        <v>0</v>
-      </c>
-      <c r="H65" s="9">
-        <v>0</v>
-      </c>
-      <c r="I65" s="9">
-        <v>0</v>
-      </c>
-      <c r="J65" s="10">
-        <f t="shared" si="9"/>
-        <v>100</v>
-      </c>
+      <c r="A65" s="1"/>
+      <c r="B65" s="1"/>
+      <c r="C65" s="1"/>
+      <c r="D65" s="1"/>
+      <c r="E65" s="1"/>
+      <c r="F65" s="1"/>
+      <c r="G65" s="1"/>
+      <c r="H65" s="1"/>
+      <c r="I65" s="1"/>
+      <c r="J65" s="1"/>
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
       <c r="M65" s="1"/>
@@ -3359,35 +2897,16 @@
       <c r="S65" s="1"/>
     </row>
     <row r="66" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="17"/>
-      <c r="B66" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="C66" s="4" t="s">
-        <v>108</v>
-      </c>
-      <c r="D66" s="9">
-        <v>100</v>
-      </c>
-      <c r="E66" s="9">
-        <v>0</v>
-      </c>
-      <c r="F66" s="9">
-        <v>0</v>
-      </c>
-      <c r="G66" s="9">
-        <v>0</v>
-      </c>
-      <c r="H66" s="9">
-        <v>0</v>
-      </c>
-      <c r="I66" s="9">
-        <v>0</v>
-      </c>
-      <c r="J66" s="10">
-        <f t="shared" si="9"/>
-        <v>100</v>
-      </c>
+      <c r="A66" s="1"/>
+      <c r="B66" s="1"/>
+      <c r="C66" s="1"/>
+      <c r="D66" s="1"/>
+      <c r="E66" s="1"/>
+      <c r="F66" s="1"/>
+      <c r="G66" s="1"/>
+      <c r="H66" s="1"/>
+      <c r="I66" s="1"/>
+      <c r="J66" s="1"/>
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
       <c r="M66" s="1"/>
@@ -3399,35 +2918,16 @@
       <c r="S66" s="1"/>
     </row>
     <row r="67" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="17"/>
-      <c r="B67" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="C67" s="4" t="s">
-        <v>110</v>
-      </c>
-      <c r="D67" s="9">
-        <v>50</v>
-      </c>
-      <c r="E67" s="9">
-        <v>0</v>
-      </c>
-      <c r="F67" s="9">
-        <v>50</v>
-      </c>
-      <c r="G67" s="9">
-        <v>0</v>
-      </c>
-      <c r="H67" s="9">
-        <v>0</v>
-      </c>
-      <c r="I67" s="9">
-        <v>0</v>
-      </c>
-      <c r="J67" s="10">
-        <f t="shared" si="9"/>
-        <v>100</v>
-      </c>
+      <c r="A67" s="1"/>
+      <c r="B67" s="1"/>
+      <c r="C67" s="1"/>
+      <c r="D67" s="1"/>
+      <c r="E67" s="1"/>
+      <c r="F67" s="1"/>
+      <c r="G67" s="1"/>
+      <c r="H67" s="1"/>
+      <c r="I67" s="1"/>
+      <c r="J67" s="1"/>
       <c r="K67" s="1"/>
       <c r="L67" s="1"/>
       <c r="M67" s="1"/>
@@ -3439,35 +2939,16 @@
       <c r="S67" s="1"/>
     </row>
     <row r="68" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="17"/>
-      <c r="B68" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="C68" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="D68" s="9">
-        <v>50</v>
-      </c>
-      <c r="E68" s="9">
-        <v>0</v>
-      </c>
-      <c r="F68" s="9">
-        <v>50</v>
-      </c>
-      <c r="G68" s="9">
-        <v>0</v>
-      </c>
-      <c r="H68" s="9">
-        <v>0</v>
-      </c>
-      <c r="I68" s="9">
-        <v>0</v>
-      </c>
-      <c r="J68" s="10">
-        <f t="shared" si="9"/>
-        <v>100</v>
-      </c>
+      <c r="A68" s="1"/>
+      <c r="B68" s="1"/>
+      <c r="C68" s="1"/>
+      <c r="D68" s="1"/>
+      <c r="E68" s="1"/>
+      <c r="F68" s="1"/>
+      <c r="G68" s="1"/>
+      <c r="H68" s="1"/>
+      <c r="I68" s="1"/>
+      <c r="J68" s="1"/>
       <c r="K68" s="1"/>
       <c r="L68" s="1"/>
       <c r="M68" s="1"/>
@@ -3479,35 +2960,16 @@
       <c r="S68" s="1"/>
     </row>
     <row r="69" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="17"/>
-      <c r="B69" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="C69" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="D69" s="9">
-        <v>100</v>
-      </c>
-      <c r="E69" s="9">
-        <v>0</v>
-      </c>
-      <c r="F69" s="9">
-        <v>0</v>
-      </c>
-      <c r="G69" s="9">
-        <v>0</v>
-      </c>
-      <c r="H69" s="9">
-        <v>0</v>
-      </c>
-      <c r="I69" s="9">
-        <v>0</v>
-      </c>
-      <c r="J69" s="10">
-        <f t="shared" si="9"/>
-        <v>100</v>
-      </c>
+      <c r="A69" s="1"/>
+      <c r="B69" s="1"/>
+      <c r="C69" s="1"/>
+      <c r="D69" s="1"/>
+      <c r="E69" s="1"/>
+      <c r="F69" s="1"/>
+      <c r="G69" s="1"/>
+      <c r="H69" s="1"/>
+      <c r="I69" s="1"/>
+      <c r="J69" s="1"/>
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
       <c r="M69" s="1"/>
@@ -3519,35 +2981,16 @@
       <c r="S69" s="1"/>
     </row>
     <row r="70" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="17"/>
-      <c r="B70" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="C70" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="D70" s="10">
-        <v>50</v>
-      </c>
-      <c r="E70" s="9">
-        <v>0</v>
-      </c>
-      <c r="F70" s="10">
-        <v>50</v>
-      </c>
-      <c r="G70" s="9">
-        <v>0</v>
-      </c>
-      <c r="H70" s="9">
-        <v>0</v>
-      </c>
-      <c r="I70" s="9">
-        <v>0</v>
-      </c>
-      <c r="J70" s="10">
-        <f t="shared" si="9"/>
-        <v>100</v>
-      </c>
+      <c r="A70" s="1"/>
+      <c r="B70" s="1"/>
+      <c r="C70" s="1"/>
+      <c r="D70" s="1"/>
+      <c r="E70" s="1"/>
+      <c r="F70" s="1"/>
+      <c r="G70" s="1"/>
+      <c r="H70" s="1"/>
+      <c r="I70" s="1"/>
+      <c r="J70" s="1"/>
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
       <c r="M70" s="1"/>
@@ -3559,35 +3002,16 @@
       <c r="S70" s="1"/>
     </row>
     <row r="71" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="17"/>
-      <c r="B71" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="C71" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="D71" s="9">
-        <v>100</v>
-      </c>
-      <c r="E71" s="9">
-        <v>0</v>
-      </c>
-      <c r="F71" s="9">
-        <v>0</v>
-      </c>
-      <c r="G71" s="9">
-        <v>0</v>
-      </c>
-      <c r="H71" s="9">
-        <v>0</v>
-      </c>
-      <c r="I71" s="9">
-        <v>0</v>
-      </c>
-      <c r="J71" s="10">
-        <f t="shared" si="9"/>
-        <v>100</v>
-      </c>
+      <c r="A71" s="1"/>
+      <c r="B71" s="1"/>
+      <c r="C71" s="1"/>
+      <c r="D71" s="1"/>
+      <c r="E71" s="1"/>
+      <c r="F71" s="1"/>
+      <c r="G71" s="1"/>
+      <c r="H71" s="1"/>
+      <c r="I71" s="1"/>
+      <c r="J71" s="1"/>
       <c r="K71" s="1"/>
       <c r="L71" s="1"/>
       <c r="M71" s="1"/>
@@ -3599,35 +3023,16 @@
       <c r="S71" s="1"/>
     </row>
     <row r="72" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="17"/>
-      <c r="B72" s="4" t="s">
-        <v>119</v>
-      </c>
-      <c r="C72" s="4" t="s">
-        <v>120</v>
-      </c>
-      <c r="D72" s="9">
-        <v>100</v>
-      </c>
-      <c r="E72" s="9">
-        <v>0</v>
-      </c>
-      <c r="F72" s="9">
-        <v>0</v>
-      </c>
-      <c r="G72" s="9">
-        <v>0</v>
-      </c>
-      <c r="H72" s="9">
-        <v>0</v>
-      </c>
-      <c r="I72" s="9">
-        <v>0</v>
-      </c>
-      <c r="J72" s="10">
-        <f t="shared" si="9"/>
-        <v>100</v>
-      </c>
+      <c r="A72" s="1"/>
+      <c r="B72" s="1"/>
+      <c r="C72" s="1"/>
+      <c r="D72" s="1"/>
+      <c r="E72" s="1"/>
+      <c r="F72" s="1"/>
+      <c r="G72" s="1"/>
+      <c r="H72" s="1"/>
+      <c r="I72" s="1"/>
+      <c r="J72" s="1"/>
       <c r="K72" s="1"/>
       <c r="L72" s="1"/>
       <c r="M72" s="1"/>
@@ -3639,33 +3044,16 @@
       <c r="S72" s="1"/>
     </row>
     <row r="73" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="17"/>
-      <c r="B73" s="4"/>
-      <c r="C73" s="4" t="s">
-        <v>71</v>
-      </c>
-      <c r="D73" s="9">
-        <v>100</v>
-      </c>
-      <c r="E73" s="9">
-        <v>0</v>
-      </c>
-      <c r="F73" s="9">
-        <v>0</v>
-      </c>
-      <c r="G73" s="9">
-        <v>0</v>
-      </c>
-      <c r="H73" s="9">
-        <v>0</v>
-      </c>
-      <c r="I73" s="9">
-        <v>0</v>
-      </c>
-      <c r="J73" s="10">
-        <f t="shared" si="9"/>
-        <v>100</v>
-      </c>
+      <c r="A73" s="1"/>
+      <c r="B73" s="1"/>
+      <c r="C73" s="1"/>
+      <c r="D73" s="1"/>
+      <c r="E73" s="1"/>
+      <c r="F73" s="1"/>
+      <c r="G73" s="1"/>
+      <c r="H73" s="1"/>
+      <c r="I73" s="1"/>
+      <c r="J73" s="1"/>
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>
       <c r="M73" s="1"/>
@@ -3677,35 +3065,16 @@
       <c r="S73" s="1"/>
     </row>
     <row r="74" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="17"/>
-      <c r="B74" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="C74" s="4" t="s">
-        <v>122</v>
-      </c>
-      <c r="D74" s="9">
-        <v>100</v>
-      </c>
-      <c r="E74" s="9">
-        <v>0</v>
-      </c>
-      <c r="F74" s="9">
-        <v>0</v>
-      </c>
-      <c r="G74" s="9">
-        <v>0</v>
-      </c>
-      <c r="H74" s="9">
-        <v>0</v>
-      </c>
-      <c r="I74" s="9">
-        <v>0</v>
-      </c>
-      <c r="J74" s="10">
-        <f t="shared" si="9"/>
-        <v>100</v>
-      </c>
+      <c r="A74" s="1"/>
+      <c r="B74" s="1"/>
+      <c r="C74" s="1"/>
+      <c r="D74" s="1"/>
+      <c r="E74" s="1"/>
+      <c r="F74" s="1"/>
+      <c r="G74" s="1"/>
+      <c r="H74" s="1"/>
+      <c r="I74" s="1"/>
+      <c r="J74" s="1"/>
       <c r="K74" s="1"/>
       <c r="L74" s="1"/>
       <c r="M74" s="1"/>
@@ -3717,35 +3086,16 @@
       <c r="S74" s="1"/>
     </row>
     <row r="75" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="17"/>
-      <c r="B75" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="C75" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="D75" s="9">
-        <v>50</v>
-      </c>
-      <c r="E75" s="9">
-        <v>0</v>
-      </c>
-      <c r="F75" s="9">
-        <v>50</v>
-      </c>
-      <c r="G75" s="9">
-        <v>0</v>
-      </c>
-      <c r="H75" s="9">
-        <v>0</v>
-      </c>
-      <c r="I75" s="9">
-        <v>0</v>
-      </c>
-      <c r="J75" s="10">
-        <f t="shared" si="9"/>
-        <v>100</v>
-      </c>
+      <c r="A75" s="1"/>
+      <c r="B75" s="1"/>
+      <c r="C75" s="1"/>
+      <c r="D75" s="1"/>
+      <c r="E75" s="1"/>
+      <c r="F75" s="1"/>
+      <c r="G75" s="1"/>
+      <c r="H75" s="1"/>
+      <c r="I75" s="1"/>
+      <c r="J75" s="1"/>
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
       <c r="M75" s="1"/>
@@ -3757,35 +3107,16 @@
       <c r="S75" s="1"/>
     </row>
     <row r="76" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="17"/>
-      <c r="B76" s="4" t="s">
-        <v>125</v>
-      </c>
-      <c r="C76" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="D76" s="9">
-        <v>100</v>
-      </c>
-      <c r="E76" s="9">
-        <v>0</v>
-      </c>
-      <c r="F76" s="9">
-        <v>0</v>
-      </c>
-      <c r="G76" s="9">
-        <v>0</v>
-      </c>
-      <c r="H76" s="9">
-        <v>0</v>
-      </c>
-      <c r="I76" s="9">
-        <v>0</v>
-      </c>
-      <c r="J76" s="10">
-        <f t="shared" si="9"/>
-        <v>100</v>
-      </c>
+      <c r="A76" s="1"/>
+      <c r="B76" s="1"/>
+      <c r="C76" s="1"/>
+      <c r="D76" s="1"/>
+      <c r="E76" s="1"/>
+      <c r="F76" s="1"/>
+      <c r="G76" s="1"/>
+      <c r="H76" s="1"/>
+      <c r="I76" s="1"/>
+      <c r="J76" s="1"/>
       <c r="K76" s="1"/>
       <c r="L76" s="1"/>
       <c r="M76" s="1"/>
@@ -3797,35 +3128,16 @@
       <c r="S76" s="1"/>
     </row>
     <row r="77" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="17"/>
-      <c r="B77" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="C77" s="4" t="s">
-        <v>128</v>
-      </c>
-      <c r="D77" s="9">
-        <v>100</v>
-      </c>
-      <c r="E77" s="9">
-        <v>0</v>
-      </c>
-      <c r="F77" s="9">
-        <v>0</v>
-      </c>
-      <c r="G77" s="9">
-        <v>0</v>
-      </c>
-      <c r="H77" s="9">
-        <v>0</v>
-      </c>
-      <c r="I77" s="9">
-        <v>0</v>
-      </c>
-      <c r="J77" s="10">
-        <f t="shared" si="9"/>
-        <v>100</v>
-      </c>
+      <c r="A77" s="1"/>
+      <c r="B77" s="1"/>
+      <c r="C77" s="1"/>
+      <c r="D77" s="1"/>
+      <c r="E77" s="1"/>
+      <c r="F77" s="1"/>
+      <c r="G77" s="1"/>
+      <c r="H77" s="1"/>
+      <c r="I77" s="1"/>
+      <c r="J77" s="1"/>
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
       <c r="M77" s="1"/>
@@ -3837,35 +3149,16 @@
       <c r="S77" s="1"/>
     </row>
     <row r="78" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="17"/>
-      <c r="B78" s="4" t="s">
-        <v>129</v>
-      </c>
-      <c r="C78" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="D78" s="9">
-        <v>100</v>
-      </c>
-      <c r="E78" s="9">
-        <v>0</v>
-      </c>
-      <c r="F78" s="9">
-        <v>0</v>
-      </c>
-      <c r="G78" s="9">
-        <v>0</v>
-      </c>
-      <c r="H78" s="9">
-        <v>0</v>
-      </c>
-      <c r="I78" s="9">
-        <v>0</v>
-      </c>
-      <c r="J78" s="10">
-        <f t="shared" si="9"/>
-        <v>100</v>
-      </c>
+      <c r="A78" s="1"/>
+      <c r="B78" s="1"/>
+      <c r="C78" s="1"/>
+      <c r="D78" s="1"/>
+      <c r="E78" s="1"/>
+      <c r="F78" s="1"/>
+      <c r="G78" s="1"/>
+      <c r="H78" s="1"/>
+      <c r="I78" s="1"/>
+      <c r="J78" s="1"/>
       <c r="K78" s="1"/>
       <c r="L78" s="1"/>
       <c r="M78" s="1"/>
@@ -3877,18 +3170,16 @@
       <c r="S78" s="1"/>
     </row>
     <row r="79" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="42" t="s">
-        <v>131</v>
-      </c>
-      <c r="B79" s="34"/>
-      <c r="C79" s="34"/>
-      <c r="D79" s="34"/>
-      <c r="E79" s="34"/>
-      <c r="F79" s="34"/>
-      <c r="G79" s="34"/>
-      <c r="H79" s="34"/>
-      <c r="I79" s="34"/>
-      <c r="J79" s="31"/>
+      <c r="A79" s="1"/>
+      <c r="B79" s="1"/>
+      <c r="C79" s="1"/>
+      <c r="D79" s="1"/>
+      <c r="E79" s="1"/>
+      <c r="F79" s="1"/>
+      <c r="G79" s="1"/>
+      <c r="H79" s="1"/>
+      <c r="I79" s="1"/>
+      <c r="J79" s="1"/>
       <c r="K79" s="1"/>
       <c r="L79" s="1"/>
       <c r="M79" s="1"/>
@@ -3900,26 +3191,16 @@
       <c r="S79" s="1"/>
     </row>
     <row r="80" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="24"/>
-      <c r="B80" s="25"/>
-      <c r="C80" s="17" t="s">
-        <v>132</v>
-      </c>
-      <c r="D80" s="32" t="s">
-        <v>133</v>
-      </c>
-      <c r="E80" s="31"/>
-      <c r="F80" s="32" t="s">
-        <v>134</v>
-      </c>
-      <c r="G80" s="31"/>
-      <c r="H80" s="32" t="s">
-        <v>135</v>
-      </c>
-      <c r="I80" s="31"/>
-      <c r="J80" s="17" t="s">
-        <v>136</v>
-      </c>
+      <c r="A80" s="1"/>
+      <c r="B80" s="1"/>
+      <c r="C80" s="1"/>
+      <c r="D80" s="1"/>
+      <c r="E80" s="1"/>
+      <c r="F80" s="1"/>
+      <c r="G80" s="1"/>
+      <c r="H80" s="1"/>
+      <c r="I80" s="1"/>
+      <c r="J80" s="1"/>
       <c r="K80" s="1"/>
       <c r="L80" s="1"/>
       <c r="M80" s="1"/>
@@ -3931,30 +3212,16 @@
       <c r="S80" s="1"/>
     </row>
     <row r="81" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="24"/>
-      <c r="B81" s="25"/>
-      <c r="C81" s="19">
-        <v>1</v>
-      </c>
-      <c r="D81" s="30" t="e">
-        <f xml:space="preserve"> SUMIF(#REF!, "SEC",#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E81" s="31"/>
-      <c r="F81" s="30" t="e">
-        <f xml:space="preserve"> SUMIF(#REF!, "VAC",#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G81" s="31"/>
-      <c r="H81" s="30" t="e">
-        <f xml:space="preserve"> SUMIF(#REF!, "RP/OJT",#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I81" s="31"/>
-      <c r="J81" s="26" t="e">
-        <f>#REF!+#REF!+#REF!+#REF!+D81+F81+H81</f>
-        <v>#REF!</v>
-      </c>
+      <c r="A81" s="1"/>
+      <c r="B81" s="1"/>
+      <c r="C81" s="1"/>
+      <c r="D81" s="1"/>
+      <c r="E81" s="1"/>
+      <c r="F81" s="1"/>
+      <c r="G81" s="1"/>
+      <c r="H81" s="1"/>
+      <c r="I81" s="1"/>
+      <c r="J81" s="1"/>
       <c r="K81" s="1"/>
       <c r="L81" s="1"/>
       <c r="M81" s="1"/>
@@ -3966,30 +3233,16 @@
       <c r="S81" s="1"/>
     </row>
     <row r="82" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="24"/>
-      <c r="B82" s="25"/>
-      <c r="C82" s="19">
-        <v>2</v>
-      </c>
-      <c r="D82" s="30" t="e">
-        <f xml:space="preserve"> SUMIF(#REF!, "SEC",#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E82" s="31"/>
-      <c r="F82" s="30" t="e">
-        <f xml:space="preserve"> SUMIF(#REF!, "VAC",#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G82" s="31"/>
-      <c r="H82" s="30" t="e">
-        <f xml:space="preserve"> SUMIF(#REF!, "RP/OJT",#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I82" s="31"/>
-      <c r="J82" s="26" t="e">
-        <f>#REF!+#REF!+#REF!+#REF!+D82+F82+H82</f>
-        <v>#REF!</v>
-      </c>
+      <c r="A82" s="1"/>
+      <c r="B82" s="1"/>
+      <c r="C82" s="1"/>
+      <c r="D82" s="1"/>
+      <c r="E82" s="1"/>
+      <c r="F82" s="1"/>
+      <c r="G82" s="1"/>
+      <c r="H82" s="1"/>
+      <c r="I82" s="1"/>
+      <c r="J82" s="1"/>
       <c r="K82" s="1"/>
       <c r="L82" s="1"/>
       <c r="M82" s="1"/>
@@ -4001,30 +3254,16 @@
       <c r="S82" s="1"/>
     </row>
     <row r="83" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="24"/>
-      <c r="B83" s="25"/>
-      <c r="C83" s="19">
-        <v>3</v>
-      </c>
-      <c r="D83" s="30" t="e">
-        <f xml:space="preserve"> SUMIF(#REF!, "SEC",#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E83" s="31"/>
-      <c r="F83" s="30" t="e">
-        <f xml:space="preserve"> SUMIF(#REF!, "VAC",#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G83" s="31"/>
-      <c r="H83" s="30" t="e">
-        <f xml:space="preserve"> SUMIF(#REF!, "RP/OJT",#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I83" s="31"/>
-      <c r="J83" s="26" t="e">
-        <f>#REF!+#REF!+#REF!+#REF!+D83+F83+H83</f>
-        <v>#REF!</v>
-      </c>
+      <c r="A83" s="1"/>
+      <c r="B83" s="1"/>
+      <c r="C83" s="1"/>
+      <c r="D83" s="1"/>
+      <c r="E83" s="1"/>
+      <c r="F83" s="1"/>
+      <c r="G83" s="1"/>
+      <c r="H83" s="1"/>
+      <c r="I83" s="1"/>
+      <c r="J83" s="1"/>
       <c r="K83" s="1"/>
       <c r="L83" s="1"/>
       <c r="M83" s="1"/>
@@ -4036,30 +3275,16 @@
       <c r="S83" s="1"/>
     </row>
     <row r="84" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="24"/>
-      <c r="B84" s="25"/>
-      <c r="C84" s="19">
-        <v>4</v>
-      </c>
-      <c r="D84" s="30" t="e">
-        <f xml:space="preserve"> SUMIF(#REF!, "SEC",#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E84" s="31"/>
-      <c r="F84" s="30" t="e">
-        <f xml:space="preserve"> SUMIF(#REF!, "VAC",#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G84" s="31"/>
-      <c r="H84" s="30" t="e">
-        <f xml:space="preserve"> SUMIF(#REF!, "RP/OJT",#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I84" s="31"/>
-      <c r="J84" s="26" t="e">
-        <f>#REF!+#REF!+#REF!+#REF!+D84+F84+H84</f>
-        <v>#REF!</v>
-      </c>
+      <c r="A84" s="1"/>
+      <c r="B84" s="1"/>
+      <c r="C84" s="1"/>
+      <c r="D84" s="1"/>
+      <c r="E84" s="1"/>
+      <c r="F84" s="1"/>
+      <c r="G84" s="1"/>
+      <c r="H84" s="1"/>
+      <c r="I84" s="1"/>
+      <c r="J84" s="1"/>
       <c r="K84" s="1"/>
       <c r="L84" s="1"/>
       <c r="M84" s="1"/>
@@ -4071,30 +3296,16 @@
       <c r="S84" s="1"/>
     </row>
     <row r="85" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="24"/>
-      <c r="B85" s="25"/>
-      <c r="C85" s="19">
-        <v>5</v>
-      </c>
-      <c r="D85" s="30" t="e">
-        <f xml:space="preserve"> SUMIF(#REF!, "SEC",#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E85" s="31"/>
-      <c r="F85" s="30" t="e">
-        <f xml:space="preserve"> SUMIF(#REF!, "VAC",#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G85" s="31"/>
-      <c r="H85" s="30" t="e">
-        <f xml:space="preserve"> SUMIF(#REF!, "RP/OJT",#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I85" s="31"/>
-      <c r="J85" s="26" t="e">
-        <f>#REF!+#REF!+#REF!+#REF!+D85+F85+H85</f>
-        <v>#REF!</v>
-      </c>
+      <c r="A85" s="1"/>
+      <c r="B85" s="1"/>
+      <c r="C85" s="1"/>
+      <c r="D85" s="1"/>
+      <c r="E85" s="1"/>
+      <c r="F85" s="1"/>
+      <c r="G85" s="1"/>
+      <c r="H85" s="1"/>
+      <c r="I85" s="1"/>
+      <c r="J85" s="1"/>
       <c r="K85" s="1"/>
       <c r="L85" s="1"/>
       <c r="M85" s="1"/>
@@ -4106,30 +3317,16 @@
       <c r="S85" s="1"/>
     </row>
     <row r="86" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="24"/>
-      <c r="B86" s="25"/>
-      <c r="C86" s="19">
-        <v>6</v>
-      </c>
-      <c r="D86" s="30" t="e">
-        <f xml:space="preserve"> SUMIF(#REF!, "SEC",#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="E86" s="31"/>
-      <c r="F86" s="30" t="e">
-        <f xml:space="preserve"> SUMIF(#REF!, "VAC",#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="G86" s="31"/>
-      <c r="H86" s="30" t="e">
-        <f xml:space="preserve"> SUMIF(#REF!, "RP/OJT",#REF!)</f>
-        <v>#REF!</v>
-      </c>
-      <c r="I86" s="31"/>
-      <c r="J86" s="26" t="e">
-        <f>#REF!+#REF!+#REF!+#REF!+D86+F86+H86</f>
-        <v>#REF!</v>
-      </c>
+      <c r="A86" s="1"/>
+      <c r="B86" s="1"/>
+      <c r="C86" s="1"/>
+      <c r="D86" s="1"/>
+      <c r="E86" s="1"/>
+      <c r="F86" s="1"/>
+      <c r="G86" s="1"/>
+      <c r="H86" s="1"/>
+      <c r="I86" s="1"/>
+      <c r="J86" s="1"/>
       <c r="K86" s="1"/>
       <c r="L86" s="1"/>
       <c r="M86" s="1"/>
@@ -4141,27 +3338,16 @@
       <c r="S86" s="1"/>
     </row>
     <row r="87" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="27"/>
-      <c r="B87" s="28"/>
-      <c r="C87" s="29" t="s">
-        <v>137</v>
-      </c>
-      <c r="D87" s="32">
-        <v>6</v>
-      </c>
-      <c r="E87" s="31"/>
-      <c r="F87" s="32">
-        <v>4</v>
-      </c>
-      <c r="G87" s="31"/>
-      <c r="H87" s="32">
-        <v>11</v>
-      </c>
-      <c r="I87" s="31"/>
-      <c r="J87" s="29" t="e">
-        <f>SUM(J81:J86)</f>
-        <v>#REF!</v>
-      </c>
+      <c r="A87" s="1"/>
+      <c r="B87" s="1"/>
+      <c r="C87" s="1"/>
+      <c r="D87" s="1"/>
+      <c r="E87" s="1"/>
+      <c r="F87" s="1"/>
+      <c r="G87" s="1"/>
+      <c r="H87" s="1"/>
+      <c r="I87" s="1"/>
+      <c r="J87" s="1"/>
       <c r="K87" s="1"/>
       <c r="L87" s="1"/>
       <c r="M87" s="1"/>
@@ -22465,908 +21651,65 @@
     </row>
     <row r="959" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A959" s="1"/>
-      <c r="B959" s="1"/>
-      <c r="C959" s="1"/>
-      <c r="D959" s="1"/>
-      <c r="E959" s="1"/>
-      <c r="F959" s="1"/>
-      <c r="G959" s="1"/>
-      <c r="H959" s="1"/>
-      <c r="I959" s="1"/>
-      <c r="J959" s="1"/>
-      <c r="K959" s="1"/>
-      <c r="L959" s="1"/>
-      <c r="M959" s="1"/>
-      <c r="N959" s="1"/>
-      <c r="O959" s="1"/>
-      <c r="P959" s="1"/>
-      <c r="Q959" s="1"/>
-      <c r="R959" s="1"/>
-      <c r="S959" s="1"/>
     </row>
     <row r="960" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A960" s="1"/>
-      <c r="B960" s="1"/>
-      <c r="C960" s="1"/>
-      <c r="D960" s="1"/>
-      <c r="E960" s="1"/>
-      <c r="F960" s="1"/>
-      <c r="G960" s="1"/>
-      <c r="H960" s="1"/>
-      <c r="I960" s="1"/>
-      <c r="J960" s="1"/>
-      <c r="K960" s="1"/>
-      <c r="L960" s="1"/>
-      <c r="M960" s="1"/>
-      <c r="N960" s="1"/>
-      <c r="O960" s="1"/>
-      <c r="P960" s="1"/>
-      <c r="Q960" s="1"/>
-      <c r="R960" s="1"/>
-      <c r="S960" s="1"/>
-    </row>
-    <row r="961" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A961" s="1"/>
-      <c r="B961" s="1"/>
-      <c r="C961" s="1"/>
-      <c r="D961" s="1"/>
-      <c r="E961" s="1"/>
-      <c r="F961" s="1"/>
-      <c r="G961" s="1"/>
-      <c r="H961" s="1"/>
-      <c r="I961" s="1"/>
-      <c r="J961" s="1"/>
-      <c r="K961" s="1"/>
-      <c r="L961" s="1"/>
-      <c r="M961" s="1"/>
-      <c r="N961" s="1"/>
-      <c r="O961" s="1"/>
-      <c r="P961" s="1"/>
-      <c r="Q961" s="1"/>
-      <c r="R961" s="1"/>
-      <c r="S961" s="1"/>
-    </row>
-    <row r="962" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A962" s="1"/>
-      <c r="B962" s="1"/>
-      <c r="C962" s="1"/>
-      <c r="D962" s="1"/>
-      <c r="E962" s="1"/>
-      <c r="F962" s="1"/>
-      <c r="G962" s="1"/>
-      <c r="H962" s="1"/>
-      <c r="I962" s="1"/>
-      <c r="J962" s="1"/>
-      <c r="K962" s="1"/>
-      <c r="L962" s="1"/>
-      <c r="M962" s="1"/>
-      <c r="N962" s="1"/>
-      <c r="O962" s="1"/>
-      <c r="P962" s="1"/>
-      <c r="Q962" s="1"/>
-      <c r="R962" s="1"/>
-      <c r="S962" s="1"/>
-    </row>
-    <row r="963" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A963" s="1"/>
-      <c r="B963" s="1"/>
-      <c r="C963" s="1"/>
-      <c r="D963" s="1"/>
-      <c r="E963" s="1"/>
-      <c r="F963" s="1"/>
-      <c r="G963" s="1"/>
-      <c r="H963" s="1"/>
-      <c r="I963" s="1"/>
-      <c r="J963" s="1"/>
-      <c r="K963" s="1"/>
-      <c r="L963" s="1"/>
-      <c r="M963" s="1"/>
-      <c r="N963" s="1"/>
-      <c r="O963" s="1"/>
-      <c r="P963" s="1"/>
-      <c r="Q963" s="1"/>
-      <c r="R963" s="1"/>
-      <c r="S963" s="1"/>
-    </row>
-    <row r="964" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A964" s="1"/>
-      <c r="B964" s="1"/>
-      <c r="C964" s="1"/>
-      <c r="D964" s="1"/>
-      <c r="E964" s="1"/>
-      <c r="F964" s="1"/>
-      <c r="G964" s="1"/>
-      <c r="H964" s="1"/>
-      <c r="I964" s="1"/>
-      <c r="J964" s="1"/>
-      <c r="K964" s="1"/>
-      <c r="L964" s="1"/>
-      <c r="M964" s="1"/>
-      <c r="N964" s="1"/>
-      <c r="O964" s="1"/>
-      <c r="P964" s="1"/>
-      <c r="Q964" s="1"/>
-      <c r="R964" s="1"/>
-      <c r="S964" s="1"/>
-    </row>
-    <row r="965" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A965" s="1"/>
-      <c r="B965" s="1"/>
-      <c r="C965" s="1"/>
-      <c r="D965" s="1"/>
-      <c r="E965" s="1"/>
-      <c r="F965" s="1"/>
-      <c r="G965" s="1"/>
-      <c r="H965" s="1"/>
-      <c r="I965" s="1"/>
-      <c r="J965" s="1"/>
-      <c r="K965" s="1"/>
-      <c r="L965" s="1"/>
-      <c r="M965" s="1"/>
-      <c r="N965" s="1"/>
-      <c r="O965" s="1"/>
-      <c r="P965" s="1"/>
-      <c r="Q965" s="1"/>
-      <c r="R965" s="1"/>
-      <c r="S965" s="1"/>
-    </row>
-    <row r="966" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A966" s="1"/>
-      <c r="B966" s="1"/>
-      <c r="C966" s="1"/>
-      <c r="D966" s="1"/>
-      <c r="E966" s="1"/>
-      <c r="F966" s="1"/>
-      <c r="G966" s="1"/>
-      <c r="H966" s="1"/>
-      <c r="I966" s="1"/>
-      <c r="J966" s="1"/>
-      <c r="K966" s="1"/>
-      <c r="L966" s="1"/>
-      <c r="M966" s="1"/>
-      <c r="N966" s="1"/>
-      <c r="O966" s="1"/>
-      <c r="P966" s="1"/>
-      <c r="Q966" s="1"/>
-      <c r="R966" s="1"/>
-      <c r="S966" s="1"/>
-    </row>
-    <row r="967" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A967" s="1"/>
-      <c r="B967" s="1"/>
-      <c r="C967" s="1"/>
-      <c r="D967" s="1"/>
-      <c r="E967" s="1"/>
-      <c r="F967" s="1"/>
-      <c r="G967" s="1"/>
-      <c r="H967" s="1"/>
-      <c r="I967" s="1"/>
-      <c r="J967" s="1"/>
-      <c r="K967" s="1"/>
-      <c r="L967" s="1"/>
-      <c r="M967" s="1"/>
-      <c r="N967" s="1"/>
-      <c r="O967" s="1"/>
-      <c r="P967" s="1"/>
-      <c r="Q967" s="1"/>
-      <c r="R967" s="1"/>
-      <c r="S967" s="1"/>
-    </row>
-    <row r="968" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A968" s="1"/>
-      <c r="B968" s="1"/>
-      <c r="C968" s="1"/>
-      <c r="D968" s="1"/>
-      <c r="E968" s="1"/>
-      <c r="F968" s="1"/>
-      <c r="G968" s="1"/>
-      <c r="H968" s="1"/>
-      <c r="I968" s="1"/>
-      <c r="J968" s="1"/>
-      <c r="K968" s="1"/>
-      <c r="L968" s="1"/>
-      <c r="M968" s="1"/>
-      <c r="N968" s="1"/>
-      <c r="O968" s="1"/>
-      <c r="P968" s="1"/>
-      <c r="Q968" s="1"/>
-      <c r="R968" s="1"/>
-      <c r="S968" s="1"/>
-    </row>
-    <row r="969" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A969" s="1"/>
-      <c r="B969" s="1"/>
-      <c r="C969" s="1"/>
-      <c r="D969" s="1"/>
-      <c r="E969" s="1"/>
-      <c r="F969" s="1"/>
-      <c r="G969" s="1"/>
-      <c r="H969" s="1"/>
-      <c r="I969" s="1"/>
-      <c r="J969" s="1"/>
-      <c r="K969" s="1"/>
-      <c r="L969" s="1"/>
-      <c r="M969" s="1"/>
-      <c r="N969" s="1"/>
-      <c r="O969" s="1"/>
-      <c r="P969" s="1"/>
-      <c r="Q969" s="1"/>
-      <c r="R969" s="1"/>
-      <c r="S969" s="1"/>
-    </row>
-    <row r="970" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A970" s="1"/>
-      <c r="B970" s="1"/>
-      <c r="C970" s="1"/>
-      <c r="D970" s="1"/>
-      <c r="E970" s="1"/>
-      <c r="F970" s="1"/>
-      <c r="G970" s="1"/>
-      <c r="H970" s="1"/>
-      <c r="I970" s="1"/>
-      <c r="J970" s="1"/>
-      <c r="K970" s="1"/>
-      <c r="L970" s="1"/>
-      <c r="M970" s="1"/>
-      <c r="N970" s="1"/>
-      <c r="O970" s="1"/>
-      <c r="P970" s="1"/>
-      <c r="Q970" s="1"/>
-      <c r="R970" s="1"/>
-      <c r="S970" s="1"/>
-    </row>
-    <row r="971" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A971" s="1"/>
-      <c r="B971" s="1"/>
-      <c r="C971" s="1"/>
-      <c r="D971" s="1"/>
-      <c r="E971" s="1"/>
-      <c r="F971" s="1"/>
-      <c r="G971" s="1"/>
-      <c r="H971" s="1"/>
-      <c r="I971" s="1"/>
-      <c r="J971" s="1"/>
-      <c r="K971" s="1"/>
-      <c r="L971" s="1"/>
-      <c r="M971" s="1"/>
-      <c r="N971" s="1"/>
-      <c r="O971" s="1"/>
-      <c r="P971" s="1"/>
-      <c r="Q971" s="1"/>
-      <c r="R971" s="1"/>
-      <c r="S971" s="1"/>
-    </row>
-    <row r="972" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A972" s="1"/>
-      <c r="B972" s="1"/>
-      <c r="C972" s="1"/>
-      <c r="D972" s="1"/>
-      <c r="E972" s="1"/>
-      <c r="F972" s="1"/>
-      <c r="G972" s="1"/>
-      <c r="H972" s="1"/>
-      <c r="I972" s="1"/>
-      <c r="J972" s="1"/>
-      <c r="K972" s="1"/>
-      <c r="L972" s="1"/>
-      <c r="M972" s="1"/>
-      <c r="N972" s="1"/>
-      <c r="O972" s="1"/>
-      <c r="P972" s="1"/>
-      <c r="Q972" s="1"/>
-      <c r="R972" s="1"/>
-      <c r="S972" s="1"/>
-    </row>
-    <row r="973" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A973" s="1"/>
-      <c r="B973" s="1"/>
-      <c r="C973" s="1"/>
-      <c r="D973" s="1"/>
-      <c r="E973" s="1"/>
-      <c r="F973" s="1"/>
-      <c r="G973" s="1"/>
-      <c r="H973" s="1"/>
-      <c r="I973" s="1"/>
-      <c r="J973" s="1"/>
-      <c r="K973" s="1"/>
-      <c r="L973" s="1"/>
-      <c r="M973" s="1"/>
-      <c r="N973" s="1"/>
-      <c r="O973" s="1"/>
-      <c r="P973" s="1"/>
-      <c r="Q973" s="1"/>
-      <c r="R973" s="1"/>
-      <c r="S973" s="1"/>
-    </row>
-    <row r="974" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A974" s="1"/>
-      <c r="B974" s="1"/>
-      <c r="C974" s="1"/>
-      <c r="D974" s="1"/>
-      <c r="E974" s="1"/>
-      <c r="F974" s="1"/>
-      <c r="G974" s="1"/>
-      <c r="H974" s="1"/>
-      <c r="I974" s="1"/>
-      <c r="J974" s="1"/>
-      <c r="K974" s="1"/>
-      <c r="L974" s="1"/>
-      <c r="M974" s="1"/>
-      <c r="N974" s="1"/>
-      <c r="O974" s="1"/>
-      <c r="P974" s="1"/>
-      <c r="Q974" s="1"/>
-      <c r="R974" s="1"/>
-      <c r="S974" s="1"/>
-    </row>
-    <row r="975" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A975" s="1"/>
-      <c r="B975" s="1"/>
-      <c r="C975" s="1"/>
-      <c r="D975" s="1"/>
-      <c r="E975" s="1"/>
-      <c r="F975" s="1"/>
-      <c r="G975" s="1"/>
-      <c r="H975" s="1"/>
-      <c r="I975" s="1"/>
-      <c r="J975" s="1"/>
-      <c r="K975" s="1"/>
-      <c r="L975" s="1"/>
-      <c r="M975" s="1"/>
-      <c r="N975" s="1"/>
-      <c r="O975" s="1"/>
-      <c r="P975" s="1"/>
-      <c r="Q975" s="1"/>
-      <c r="R975" s="1"/>
-      <c r="S975" s="1"/>
-    </row>
-    <row r="976" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A976" s="1"/>
-      <c r="B976" s="1"/>
-      <c r="C976" s="1"/>
-      <c r="D976" s="1"/>
-      <c r="E976" s="1"/>
-      <c r="F976" s="1"/>
-      <c r="G976" s="1"/>
-      <c r="H976" s="1"/>
-      <c r="I976" s="1"/>
-      <c r="J976" s="1"/>
-      <c r="K976" s="1"/>
-      <c r="L976" s="1"/>
-      <c r="M976" s="1"/>
-      <c r="N976" s="1"/>
-      <c r="O976" s="1"/>
-      <c r="P976" s="1"/>
-      <c r="Q976" s="1"/>
-      <c r="R976" s="1"/>
-      <c r="S976" s="1"/>
-    </row>
-    <row r="977" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A977" s="1"/>
-      <c r="B977" s="1"/>
-      <c r="C977" s="1"/>
-      <c r="D977" s="1"/>
-      <c r="E977" s="1"/>
-      <c r="F977" s="1"/>
-      <c r="G977" s="1"/>
-      <c r="H977" s="1"/>
-      <c r="I977" s="1"/>
-      <c r="J977" s="1"/>
-      <c r="K977" s="1"/>
-      <c r="L977" s="1"/>
-      <c r="M977" s="1"/>
-      <c r="N977" s="1"/>
-      <c r="O977" s="1"/>
-      <c r="P977" s="1"/>
-      <c r="Q977" s="1"/>
-      <c r="R977" s="1"/>
-      <c r="S977" s="1"/>
-    </row>
-    <row r="978" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A978" s="1"/>
-      <c r="B978" s="1"/>
-      <c r="C978" s="1"/>
-      <c r="D978" s="1"/>
-      <c r="E978" s="1"/>
-      <c r="F978" s="1"/>
-      <c r="G978" s="1"/>
-      <c r="H978" s="1"/>
-      <c r="I978" s="1"/>
-      <c r="J978" s="1"/>
-      <c r="K978" s="1"/>
-      <c r="L978" s="1"/>
-      <c r="M978" s="1"/>
-      <c r="N978" s="1"/>
-      <c r="O978" s="1"/>
-      <c r="P978" s="1"/>
-      <c r="Q978" s="1"/>
-      <c r="R978" s="1"/>
-      <c r="S978" s="1"/>
-    </row>
-    <row r="979" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A979" s="1"/>
-      <c r="B979" s="1"/>
-      <c r="C979" s="1"/>
-      <c r="D979" s="1"/>
-      <c r="E979" s="1"/>
-      <c r="F979" s="1"/>
-      <c r="G979" s="1"/>
-      <c r="H979" s="1"/>
-      <c r="I979" s="1"/>
-      <c r="J979" s="1"/>
-      <c r="K979" s="1"/>
-      <c r="L979" s="1"/>
-      <c r="M979" s="1"/>
-      <c r="N979" s="1"/>
-      <c r="O979" s="1"/>
-      <c r="P979" s="1"/>
-      <c r="Q979" s="1"/>
-      <c r="R979" s="1"/>
-      <c r="S979" s="1"/>
-    </row>
-    <row r="980" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A980" s="1"/>
-      <c r="B980" s="1"/>
-      <c r="C980" s="1"/>
-      <c r="D980" s="1"/>
-      <c r="E980" s="1"/>
-      <c r="F980" s="1"/>
-      <c r="G980" s="1"/>
-      <c r="H980" s="1"/>
-      <c r="I980" s="1"/>
-      <c r="J980" s="1"/>
-      <c r="K980" s="1"/>
-      <c r="L980" s="1"/>
-      <c r="M980" s="1"/>
-      <c r="N980" s="1"/>
-      <c r="O980" s="1"/>
-      <c r="P980" s="1"/>
-      <c r="Q980" s="1"/>
-      <c r="R980" s="1"/>
-      <c r="S980" s="1"/>
-    </row>
-    <row r="981" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A981" s="1"/>
-      <c r="B981" s="1"/>
-      <c r="C981" s="1"/>
-      <c r="D981" s="1"/>
-      <c r="E981" s="1"/>
-      <c r="F981" s="1"/>
-      <c r="G981" s="1"/>
-      <c r="H981" s="1"/>
-      <c r="I981" s="1"/>
-      <c r="J981" s="1"/>
-      <c r="K981" s="1"/>
-      <c r="L981" s="1"/>
-      <c r="M981" s="1"/>
-      <c r="N981" s="1"/>
-      <c r="O981" s="1"/>
-      <c r="P981" s="1"/>
-      <c r="Q981" s="1"/>
-      <c r="R981" s="1"/>
-      <c r="S981" s="1"/>
-    </row>
-    <row r="982" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A982" s="1"/>
-      <c r="B982" s="1"/>
-      <c r="C982" s="1"/>
-      <c r="D982" s="1"/>
-      <c r="E982" s="1"/>
-      <c r="F982" s="1"/>
-      <c r="G982" s="1"/>
-      <c r="H982" s="1"/>
-      <c r="I982" s="1"/>
-      <c r="J982" s="1"/>
-      <c r="K982" s="1"/>
-      <c r="L982" s="1"/>
-      <c r="M982" s="1"/>
-      <c r="N982" s="1"/>
-      <c r="O982" s="1"/>
-      <c r="P982" s="1"/>
-      <c r="Q982" s="1"/>
-      <c r="R982" s="1"/>
-      <c r="S982" s="1"/>
-    </row>
-    <row r="983" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A983" s="1"/>
-      <c r="B983" s="1"/>
-      <c r="C983" s="1"/>
-      <c r="D983" s="1"/>
-      <c r="E983" s="1"/>
-      <c r="F983" s="1"/>
-      <c r="G983" s="1"/>
-      <c r="H983" s="1"/>
-      <c r="I983" s="1"/>
-      <c r="J983" s="1"/>
-      <c r="K983" s="1"/>
-      <c r="L983" s="1"/>
-      <c r="M983" s="1"/>
-      <c r="N983" s="1"/>
-      <c r="O983" s="1"/>
-      <c r="P983" s="1"/>
-      <c r="Q983" s="1"/>
-      <c r="R983" s="1"/>
-      <c r="S983" s="1"/>
-    </row>
-    <row r="984" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A984" s="1"/>
-      <c r="B984" s="1"/>
-      <c r="C984" s="1"/>
-      <c r="D984" s="1"/>
-      <c r="E984" s="1"/>
-      <c r="F984" s="1"/>
-      <c r="G984" s="1"/>
-      <c r="H984" s="1"/>
-      <c r="I984" s="1"/>
-      <c r="J984" s="1"/>
-      <c r="K984" s="1"/>
-      <c r="L984" s="1"/>
-      <c r="M984" s="1"/>
-      <c r="N984" s="1"/>
-      <c r="O984" s="1"/>
-      <c r="P984" s="1"/>
-      <c r="Q984" s="1"/>
-      <c r="R984" s="1"/>
-      <c r="S984" s="1"/>
-    </row>
-    <row r="985" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A985" s="1"/>
-      <c r="B985" s="1"/>
-      <c r="C985" s="1"/>
-      <c r="D985" s="1"/>
-      <c r="E985" s="1"/>
-      <c r="F985" s="1"/>
-      <c r="G985" s="1"/>
-      <c r="H985" s="1"/>
-      <c r="I985" s="1"/>
-      <c r="J985" s="1"/>
-      <c r="K985" s="1"/>
-      <c r="L985" s="1"/>
-      <c r="M985" s="1"/>
-      <c r="N985" s="1"/>
-      <c r="O985" s="1"/>
-      <c r="P985" s="1"/>
-      <c r="Q985" s="1"/>
-      <c r="R985" s="1"/>
-      <c r="S985" s="1"/>
-    </row>
-    <row r="986" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A986" s="1"/>
-      <c r="B986" s="1"/>
-      <c r="C986" s="1"/>
-      <c r="D986" s="1"/>
-      <c r="E986" s="1"/>
-      <c r="F986" s="1"/>
-      <c r="G986" s="1"/>
-      <c r="H986" s="1"/>
-      <c r="I986" s="1"/>
-      <c r="J986" s="1"/>
-      <c r="K986" s="1"/>
-      <c r="L986" s="1"/>
-      <c r="M986" s="1"/>
-      <c r="N986" s="1"/>
-      <c r="O986" s="1"/>
-      <c r="P986" s="1"/>
-      <c r="Q986" s="1"/>
-      <c r="R986" s="1"/>
-      <c r="S986" s="1"/>
-    </row>
-    <row r="987" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A987" s="1"/>
-      <c r="B987" s="1"/>
-      <c r="C987" s="1"/>
-      <c r="D987" s="1"/>
-      <c r="E987" s="1"/>
-      <c r="F987" s="1"/>
-      <c r="G987" s="1"/>
-      <c r="H987" s="1"/>
-      <c r="I987" s="1"/>
-      <c r="J987" s="1"/>
-      <c r="K987" s="1"/>
-      <c r="L987" s="1"/>
-      <c r="M987" s="1"/>
-      <c r="N987" s="1"/>
-      <c r="O987" s="1"/>
-      <c r="P987" s="1"/>
-      <c r="Q987" s="1"/>
-      <c r="R987" s="1"/>
-      <c r="S987" s="1"/>
-    </row>
-    <row r="988" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A988" s="1"/>
-      <c r="B988" s="1"/>
-      <c r="C988" s="1"/>
-      <c r="D988" s="1"/>
-      <c r="E988" s="1"/>
-      <c r="F988" s="1"/>
-      <c r="G988" s="1"/>
-      <c r="H988" s="1"/>
-      <c r="I988" s="1"/>
-      <c r="J988" s="1"/>
-      <c r="K988" s="1"/>
-      <c r="L988" s="1"/>
-      <c r="M988" s="1"/>
-      <c r="N988" s="1"/>
-      <c r="O988" s="1"/>
-      <c r="P988" s="1"/>
-      <c r="Q988" s="1"/>
-      <c r="R988" s="1"/>
-      <c r="S988" s="1"/>
-    </row>
-    <row r="989" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A989" s="1"/>
-      <c r="B989" s="1"/>
-      <c r="C989" s="1"/>
-      <c r="D989" s="1"/>
-      <c r="E989" s="1"/>
-      <c r="F989" s="1"/>
-      <c r="G989" s="1"/>
-      <c r="H989" s="1"/>
-      <c r="I989" s="1"/>
-      <c r="J989" s="1"/>
-      <c r="K989" s="1"/>
-      <c r="L989" s="1"/>
-      <c r="M989" s="1"/>
-      <c r="N989" s="1"/>
-      <c r="O989" s="1"/>
-      <c r="P989" s="1"/>
-      <c r="Q989" s="1"/>
-      <c r="R989" s="1"/>
-      <c r="S989" s="1"/>
-    </row>
-    <row r="990" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A990" s="1"/>
-      <c r="B990" s="1"/>
-      <c r="C990" s="1"/>
-      <c r="D990" s="1"/>
-      <c r="E990" s="1"/>
-      <c r="F990" s="1"/>
-      <c r="G990" s="1"/>
-      <c r="H990" s="1"/>
-      <c r="I990" s="1"/>
-      <c r="J990" s="1"/>
-      <c r="K990" s="1"/>
-      <c r="L990" s="1"/>
-      <c r="M990" s="1"/>
-      <c r="N990" s="1"/>
-      <c r="O990" s="1"/>
-      <c r="P990" s="1"/>
-      <c r="Q990" s="1"/>
-      <c r="R990" s="1"/>
-      <c r="S990" s="1"/>
-    </row>
-    <row r="991" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A991" s="1"/>
-      <c r="B991" s="1"/>
-      <c r="C991" s="1"/>
-      <c r="D991" s="1"/>
-      <c r="E991" s="1"/>
-      <c r="F991" s="1"/>
-      <c r="G991" s="1"/>
-      <c r="H991" s="1"/>
-      <c r="I991" s="1"/>
-      <c r="J991" s="1"/>
-      <c r="K991" s="1"/>
-      <c r="L991" s="1"/>
-      <c r="M991" s="1"/>
-      <c r="N991" s="1"/>
-      <c r="O991" s="1"/>
-      <c r="P991" s="1"/>
-      <c r="Q991" s="1"/>
-      <c r="R991" s="1"/>
-      <c r="S991" s="1"/>
-    </row>
-    <row r="992" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A992" s="1"/>
-      <c r="B992" s="1"/>
-      <c r="C992" s="1"/>
-      <c r="D992" s="1"/>
-      <c r="E992" s="1"/>
-      <c r="F992" s="1"/>
-      <c r="G992" s="1"/>
-      <c r="H992" s="1"/>
-      <c r="I992" s="1"/>
-      <c r="J992" s="1"/>
-      <c r="K992" s="1"/>
-      <c r="L992" s="1"/>
-      <c r="M992" s="1"/>
-      <c r="N992" s="1"/>
-      <c r="O992" s="1"/>
-      <c r="P992" s="1"/>
-      <c r="Q992" s="1"/>
-      <c r="R992" s="1"/>
-      <c r="S992" s="1"/>
-    </row>
-    <row r="993" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A993" s="1"/>
-      <c r="B993" s="1"/>
-      <c r="C993" s="1"/>
-      <c r="D993" s="1"/>
-      <c r="E993" s="1"/>
-      <c r="F993" s="1"/>
-      <c r="G993" s="1"/>
-      <c r="H993" s="1"/>
-      <c r="I993" s="1"/>
-      <c r="J993" s="1"/>
-      <c r="K993" s="1"/>
-      <c r="L993" s="1"/>
-      <c r="M993" s="1"/>
-      <c r="N993" s="1"/>
-      <c r="O993" s="1"/>
-      <c r="P993" s="1"/>
-      <c r="Q993" s="1"/>
-      <c r="R993" s="1"/>
-      <c r="S993" s="1"/>
-    </row>
-    <row r="994" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A994" s="1"/>
-      <c r="B994" s="1"/>
-      <c r="C994" s="1"/>
-      <c r="D994" s="1"/>
-      <c r="E994" s="1"/>
-      <c r="F994" s="1"/>
-      <c r="G994" s="1"/>
-      <c r="H994" s="1"/>
-      <c r="I994" s="1"/>
-      <c r="J994" s="1"/>
-      <c r="K994" s="1"/>
-      <c r="L994" s="1"/>
-      <c r="M994" s="1"/>
-      <c r="N994" s="1"/>
-      <c r="O994" s="1"/>
-      <c r="P994" s="1"/>
-      <c r="Q994" s="1"/>
-      <c r="R994" s="1"/>
-      <c r="S994" s="1"/>
-    </row>
-    <row r="995" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A995" s="1"/>
-      <c r="B995" s="1"/>
-      <c r="C995" s="1"/>
-      <c r="D995" s="1"/>
-      <c r="E995" s="1"/>
-      <c r="F995" s="1"/>
-      <c r="G995" s="1"/>
-      <c r="H995" s="1"/>
-      <c r="I995" s="1"/>
-      <c r="J995" s="1"/>
-      <c r="K995" s="1"/>
-      <c r="L995" s="1"/>
-      <c r="M995" s="1"/>
-      <c r="N995" s="1"/>
-      <c r="O995" s="1"/>
-      <c r="P995" s="1"/>
-      <c r="Q995" s="1"/>
-      <c r="R995" s="1"/>
-      <c r="S995" s="1"/>
-    </row>
-    <row r="996" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A996" s="1"/>
-      <c r="B996" s="1"/>
-      <c r="C996" s="1"/>
-      <c r="D996" s="1"/>
-      <c r="E996" s="1"/>
-      <c r="F996" s="1"/>
-      <c r="G996" s="1"/>
-      <c r="H996" s="1"/>
-      <c r="I996" s="1"/>
-      <c r="J996" s="1"/>
-      <c r="K996" s="1"/>
-      <c r="L996" s="1"/>
-      <c r="M996" s="1"/>
-      <c r="N996" s="1"/>
-      <c r="O996" s="1"/>
-      <c r="P996" s="1"/>
-      <c r="Q996" s="1"/>
-      <c r="R996" s="1"/>
-      <c r="S996" s="1"/>
-    </row>
-    <row r="997" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A997" s="1"/>
-      <c r="B997" s="1"/>
-      <c r="C997" s="1"/>
-      <c r="D997" s="1"/>
-      <c r="E997" s="1"/>
-      <c r="F997" s="1"/>
-      <c r="G997" s="1"/>
-      <c r="H997" s="1"/>
-      <c r="I997" s="1"/>
-      <c r="J997" s="1"/>
-      <c r="K997" s="1"/>
-      <c r="L997" s="1"/>
-      <c r="M997" s="1"/>
-      <c r="N997" s="1"/>
-      <c r="O997" s="1"/>
-      <c r="P997" s="1"/>
-      <c r="Q997" s="1"/>
-      <c r="R997" s="1"/>
-      <c r="S997" s="1"/>
-    </row>
-    <row r="998" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A998" s="1"/>
-      <c r="B998" s="1"/>
-      <c r="C998" s="1"/>
-      <c r="D998" s="1"/>
-      <c r="E998" s="1"/>
-      <c r="F998" s="1"/>
-      <c r="G998" s="1"/>
-      <c r="H998" s="1"/>
-      <c r="I998" s="1"/>
-      <c r="J998" s="1"/>
-      <c r="K998" s="1"/>
-      <c r="L998" s="1"/>
-      <c r="M998" s="1"/>
-      <c r="N998" s="1"/>
-      <c r="O998" s="1"/>
-      <c r="P998" s="1"/>
-      <c r="Q998" s="1"/>
-      <c r="R998" s="1"/>
-      <c r="S998" s="1"/>
-    </row>
-    <row r="999" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A999" s="1"/>
-      <c r="B999" s="1"/>
-      <c r="C999" s="1"/>
-      <c r="D999" s="1"/>
-      <c r="E999" s="1"/>
-      <c r="F999" s="1"/>
-      <c r="G999" s="1"/>
-      <c r="H999" s="1"/>
-      <c r="I999" s="1"/>
-      <c r="J999" s="1"/>
-      <c r="K999" s="1"/>
-      <c r="L999" s="1"/>
-      <c r="M999" s="1"/>
-      <c r="N999" s="1"/>
-      <c r="O999" s="1"/>
-      <c r="P999" s="1"/>
-      <c r="Q999" s="1"/>
-      <c r="R999" s="1"/>
-      <c r="S999" s="1"/>
-    </row>
-    <row r="1000" spans="1:19" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1000" s="1"/>
-      <c r="B1000" s="1"/>
-      <c r="C1000" s="1"/>
-      <c r="D1000" s="1"/>
-      <c r="E1000" s="1"/>
-      <c r="F1000" s="1"/>
-      <c r="G1000" s="1"/>
-      <c r="H1000" s="1"/>
-      <c r="I1000" s="1"/>
-      <c r="J1000" s="1"/>
-      <c r="K1000" s="1"/>
-      <c r="L1000" s="1"/>
-      <c r="M1000" s="1"/>
-      <c r="N1000" s="1"/>
-      <c r="O1000" s="1"/>
-      <c r="P1000" s="1"/>
-      <c r="Q1000" s="1"/>
-      <c r="R1000" s="1"/>
-      <c r="S1000" s="1"/>
-    </row>
+    </row>
+    <row r="961" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="962" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="963" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="964" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="965" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="966" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="967" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="968" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="969" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="970" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="971" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="972" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="973" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="974" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="975" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="976" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="977" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="978" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="979" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="980" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="981" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="982" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="983" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="984" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="985" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="986" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="987" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="988" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="989" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="990" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="991" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="992" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="993" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="994" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="995" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="996" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="997" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="998" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="999" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="1000" ht="30" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <mergeCells count="51">
-    <mergeCell ref="A79:J79"/>
-    <mergeCell ref="D34:I34"/>
-    <mergeCell ref="D43:I43"/>
-    <mergeCell ref="D48:I48"/>
-    <mergeCell ref="D4:J4"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
+  <mergeCells count="25">
+    <mergeCell ref="A28:A34"/>
+    <mergeCell ref="A35:A43"/>
+    <mergeCell ref="A44:A49"/>
+    <mergeCell ref="A7:A13"/>
     <mergeCell ref="H5:I5"/>
     <mergeCell ref="D13:I13"/>
     <mergeCell ref="D20:I20"/>
     <mergeCell ref="D27:I27"/>
     <mergeCell ref="A21:A27"/>
-    <mergeCell ref="A28:A34"/>
-    <mergeCell ref="A35:A43"/>
-    <mergeCell ref="A44:A49"/>
-    <mergeCell ref="A7:A13"/>
+    <mergeCell ref="B43:C43"/>
     <mergeCell ref="A14:A20"/>
     <mergeCell ref="B27:C27"/>
     <mergeCell ref="B34:C34"/>
-    <mergeCell ref="B43:C43"/>
     <mergeCell ref="A1:J1"/>
     <mergeCell ref="A2:J2"/>
     <mergeCell ref="A3:J3"/>
@@ -23374,40 +21717,18 @@
     <mergeCell ref="B4:B6"/>
     <mergeCell ref="C4:C6"/>
     <mergeCell ref="J5:J6"/>
-    <mergeCell ref="H87:I87"/>
-    <mergeCell ref="D84:E84"/>
-    <mergeCell ref="F84:G84"/>
-    <mergeCell ref="H84:I84"/>
-    <mergeCell ref="H85:I85"/>
-    <mergeCell ref="D85:E85"/>
-    <mergeCell ref="F85:G85"/>
-    <mergeCell ref="D86:E86"/>
-    <mergeCell ref="F86:G86"/>
-    <mergeCell ref="D87:E87"/>
-    <mergeCell ref="F87:G87"/>
-    <mergeCell ref="H83:I83"/>
-    <mergeCell ref="H86:I86"/>
-    <mergeCell ref="D83:E83"/>
-    <mergeCell ref="F83:G83"/>
-    <mergeCell ref="D81:E81"/>
-    <mergeCell ref="D82:E82"/>
-    <mergeCell ref="F82:G82"/>
-    <mergeCell ref="H82:I82"/>
-    <mergeCell ref="D80:E80"/>
-    <mergeCell ref="F80:G80"/>
-    <mergeCell ref="H80:I80"/>
-    <mergeCell ref="F81:G81"/>
-    <mergeCell ref="H81:I81"/>
+    <mergeCell ref="D34:I34"/>
+    <mergeCell ref="D43:I43"/>
+    <mergeCell ref="D4:J4"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.19685039370078741" right="0.19685039370078741" top="0.39370078740157483" bottom="0.19685039370078741" header="0" footer="0"/>
   <pageSetup paperSize="9" orientation="landscape"/>
-  <rowBreaks count="5" manualBreakCount="5">
-    <brk id="49" man="1"/>
+  <rowBreaks count="2" manualBreakCount="2">
     <brk id="34" man="1"/>
     <brk id="20" man="1"/>
-    <brk id="78" man="1"/>
-    <brk id="62" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>